--- a/RNR_수입원가_2026_20260618.xlsx
+++ b/RNR_수입원가_2026_20260618.xlsx
@@ -14,9 +14,9 @@
     <sheet name="환율" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="RemitTable1">'외화송금내역'!$A$3:$L$44</definedName>
-    <definedName name="RemitTable2">'외화송금내역'!$A$47:$L$101</definedName>
     <definedName name="FxRateTable">환율!$A$7:$D$43</definedName>
+    <definedName name="RemitTable1">'외화송금내역'!$A$3:$L$40</definedName>
+    <definedName name="RemitTable2">'외화송금내역'!$A$43:$L$97</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -1580,11 +1580,6 @@
     </comment>
     <comment ref="D5" authorId="0" shapeId="0">
       <text>
-        <t>출금내역만 확인. PO/송금확인서 미확인</t>
-      </text>
-    </comment>
-    <comment ref="D6" authorId="0" shapeId="0">
-      <text>
         <t>출금내역만 확인. 송금확인서 미확인</t>
       </text>
     </comment>
@@ -10590,19 +10585,6 @@
       <c r="AE79" s="39" t="n"/>
       <c r="AF79" s="39" t="n"/>
     </row>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
     <row r="93">
       <c r="M93" s="40" t="n"/>
     </row>
@@ -11827,50 +11809,6 @@
       </c>
       <c r="L25" s="228" t="n"/>
     </row>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
     <row r="70">
       <c r="M70" s="40" t="n"/>
     </row>
@@ -13537,38 +13475,6 @@
       </c>
       <c r="J38" s="292" t="inlineStr"/>
     </row>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
     <row r="71">
       <c r="M71" s="40" t="n"/>
     </row>
@@ -13588,7 +13494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M101"/>
+  <dimension ref="A1:M98"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="12.83203125" customWidth="1" style="160" min="1" max="1"/>
@@ -13791,16 +13697,16 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Thali Consulting</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>(PO미기재)</t>
+          <t>CPO-669</t>
         </is>
       </c>
       <c r="E5" s="33" t="n">
-        <v>9247.690000000001</v>
+        <v>7410</v>
       </c>
       <c r="F5" s="7" t="n">
         <v>0</v>
@@ -13833,7 +13739,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2025.12.02</t>
+          <t>2025.12.09</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -13843,26 +13749,26 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>CPO-669</t>
+          <t>CPO675,677,CPO-664-2</t>
         </is>
       </c>
       <c r="E6" s="33" t="n">
-        <v>7410</v>
+        <v>6024</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>0</v>
+        <v>1473.3</v>
       </c>
       <c r="G6" s="33" t="n">
         <v>20</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0</v>
+        <v>8922625</v>
       </c>
       <c r="K6" s="9">
         <f>ROUND((E6+G6)*F6+H6+I6,0)</f>
@@ -13885,19 +13791,19 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>CPO675,677,CPO-664-2</t>
+          <t>GPO449,450,452,453,454</t>
         </is>
       </c>
       <c r="E7" s="33" t="n">
-        <v>6024</v>
+        <v>7862</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>1473.3</v>
+        <v>1473.2</v>
       </c>
       <c r="G7" s="33" t="n">
         <v>20</v>
@@ -13909,7 +13815,7 @@
         <v>8000</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>8922625</v>
+        <v>11629762</v>
       </c>
       <c r="K7" s="9">
         <f>ROUND((E7+G7)*F7+H7+I7,0)</f>
@@ -13927,24 +13833,24 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>2025.12.09</t>
+          <t>2025.12.16</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>GPO449,450,452,453,454</t>
+          <t>MPO-65,64</t>
         </is>
       </c>
       <c r="E8" s="33" t="n">
-        <v>7862</v>
+        <v>15040</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>1473.2</v>
+        <v>1480</v>
       </c>
       <c r="G8" s="33" t="n">
         <v>20</v>
@@ -13956,7 +13862,7 @@
         <v>8000</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>11629762</v>
+        <v>22306800</v>
       </c>
       <c r="K8" s="9">
         <f>ROUND((E8+G8)*F8+H8+I8,0)</f>
@@ -13979,31 +13885,31 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>MPO-65,64</t>
+          <t>CPO-679,CPO-678-1</t>
         </is>
       </c>
       <c r="E9" s="33" t="n">
-        <v>15040</v>
+        <v>143557</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>1480</v>
+        <v>1479.7</v>
       </c>
       <c r="G9" s="33" t="n">
         <v>20</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>10000</v>
+        <v>12500</v>
       </c>
       <c r="I9" s="9" t="n">
         <v>8000</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>22306800</v>
+        <v>212471386</v>
       </c>
       <c r="K9" s="9">
         <f>ROUND((E9+G9)*F9+H9+I9,0)</f>
@@ -14021,36 +13927,36 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>2025.12.16</t>
+          <t>2025.12.29</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>CPO-679,CPO-678-1</t>
+          <t>GPO451,458,455,456,457</t>
         </is>
       </c>
       <c r="E10" s="33" t="n">
-        <v>143557</v>
+        <v>13860</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>1479.7</v>
+        <v>1439.1</v>
       </c>
       <c r="G10" s="33" t="n">
         <v>20</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>12500</v>
+        <v>10000</v>
       </c>
       <c r="I10" s="9" t="n">
         <v>8000</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>212471386</v>
+        <v>18264679</v>
       </c>
       <c r="K10" s="9">
         <f>ROUND((E10+G10)*F10+H10+I10,0)</f>
@@ -14068,36 +13974,36 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>2025.12.19</t>
+          <t>2025.12.30</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>GDC(라이센스)</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>/ROC/라이센스</t>
+          <t>CPO676</t>
         </is>
       </c>
       <c r="E11" s="33" t="n">
-        <v>1200</v>
+        <v>36060</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>1464.9</v>
+        <v>1442.7</v>
       </c>
       <c r="G11" s="33" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>0</v>
+        <v>12500</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0</v>
+        <v>52073116</v>
       </c>
       <c r="K11" s="9">
         <f>ROUND((E11+G11)*F11+H11+I11,0)</f>
@@ -14115,36 +14021,36 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>2025.12.29</t>
+          <t>2026.01.13</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>GPO451,458,455,456,457</t>
+          <t>CPO680</t>
         </is>
       </c>
       <c r="E12" s="33" t="n">
-        <v>13860</v>
+        <v>252</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>1439.1</v>
+        <v>1479</v>
       </c>
       <c r="G12" s="33" t="n">
         <v>20</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>10000</v>
+        <v>2500</v>
       </c>
       <c r="I12" s="9" t="n">
         <v>8000</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>18264679</v>
+        <v>412788</v>
       </c>
       <c r="K12" s="9">
         <f>ROUND((E12+G12)*F12+H12+I12,0)</f>
@@ -14162,36 +14068,36 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2025.12.30</t>
+          <t>2026.01.21</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>CPO676</t>
+          <t>GPO459,460,461</t>
         </is>
       </c>
       <c r="E13" s="33" t="n">
-        <v>36060</v>
+        <v>3700</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>1442.7</v>
+        <v>1475.7</v>
       </c>
       <c r="G13" s="33" t="n">
         <v>20</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>12500</v>
+        <v>7500</v>
       </c>
       <c r="I13" s="9" t="n">
         <v>8000</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>52073116</v>
+        <v>5505104</v>
       </c>
       <c r="K13" s="9">
         <f>ROUND((E13+G13)*F13+H13+I13,0)</f>
@@ -14209,36 +14115,36 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>2026.01.13</t>
+          <t>2026.01.21</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>CPO680</t>
+          <t>MPO-66</t>
         </is>
       </c>
       <c r="E14" s="33" t="n">
-        <v>252</v>
+        <v>9626.35</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>1479</v>
+        <v>1476</v>
       </c>
       <c r="G14" s="33" t="n">
         <v>20</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>2500</v>
+        <v>10000</v>
       </c>
       <c r="I14" s="9" t="n">
         <v>8000</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>412788</v>
+        <v>14256012</v>
       </c>
       <c r="K14" s="9">
         <f>ROUND((E14+G14)*F14+H14+I14,0)</f>
@@ -14256,36 +14162,36 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026.01.21</t>
+          <t>2026.01.30</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Lemon</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>GPO459,460,461</t>
+          <t>LPO-001</t>
         </is>
       </c>
       <c r="E15" s="33" t="n">
-        <v>3700</v>
+        <v>5056.8</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>1475.7</v>
+        <v>1445.5</v>
       </c>
       <c r="G15" s="33" t="n">
         <v>20</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>7500</v>
+        <v>10000</v>
       </c>
       <c r="I15" s="9" t="n">
         <v>8000</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>5505104</v>
+        <v>7356514</v>
       </c>
       <c r="K15" s="9">
         <f>ROUND((E15+G15)*F15+H15+I15,0)</f>
@@ -14303,36 +14209,36 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>2026.01.21</t>
+          <t>2026.01.30</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>Monoplex</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>MPO-66</t>
+          <t>MONOPLEX20260126-01</t>
         </is>
       </c>
       <c r="E16" s="33" t="n">
-        <v>9626.35</v>
+        <v>25976</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>1476</v>
+        <v>1445.5</v>
       </c>
       <c r="G16" s="33" t="n">
         <v>20</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>10000</v>
+        <v>12500</v>
       </c>
       <c r="I16" s="9" t="n">
         <v>8000</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>14256012</v>
+        <v>37597718</v>
       </c>
       <c r="K16" s="9">
         <f>ROUND((E16+G16)*F16+H16+I16,0)</f>
@@ -14350,36 +14256,36 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>2026.01.30</t>
+          <t>2026.02.04</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Lemon</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>LPO-001</t>
+          <t>CPO-682,683</t>
         </is>
       </c>
       <c r="E17" s="33" t="n">
-        <v>5056.8</v>
+        <v>24794</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>1445.5</v>
+        <v>1454.7</v>
       </c>
       <c r="G17" s="33" t="n">
         <v>20</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>10000</v>
+        <v>12500</v>
       </c>
       <c r="I17" s="9" t="n">
         <v>8000</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>7356514</v>
+        <v>36117425</v>
       </c>
       <c r="K17" s="9">
         <f>ROUND((E17+G17)*F17+H17+I17,0)</f>
@@ -14397,36 +14303,36 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>2026.01.30</t>
+          <t>2026.02.04</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Monoplex</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>MONOPLEX20260126-01</t>
+          <t>GPO462,463,464</t>
         </is>
       </c>
       <c r="E18" s="33" t="n">
-        <v>25976</v>
+        <v>11599.57</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>1445.5</v>
+        <v>1453.6</v>
       </c>
       <c r="G18" s="33" t="n">
         <v>20</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>12500</v>
+        <v>10000</v>
       </c>
       <c r="I18" s="9" t="n">
         <v>8000</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>37597718</v>
+        <v>16908206</v>
       </c>
       <c r="K18" s="9">
         <f>ROUND((E18+G18)*F18+H18+I18,0)</f>
@@ -14444,7 +14350,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>2026.02.04</t>
+          <t>2026.02.11</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -14454,14 +14360,14 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>CPO-682,683</t>
+          <t>CPO681</t>
         </is>
       </c>
       <c r="E19" s="33" t="n">
-        <v>24794</v>
+        <v>26358</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>1454.7</v>
+        <v>1460.7</v>
       </c>
       <c r="G19" s="33" t="n">
         <v>20</v>
@@ -14473,7 +14379,7 @@
         <v>8000</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>36117425</v>
+        <v>38550844</v>
       </c>
       <c r="K19" s="9">
         <f>ROUND((E19+G19)*F19+H19+I19,0)</f>
@@ -14491,24 +14397,24 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>2026.02.04</t>
+          <t>2026.02.19</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>GPO462,463,464</t>
+          <t>CPO686,CPO689</t>
         </is>
       </c>
       <c r="E20" s="33" t="n">
-        <v>11599.57</v>
+        <v>17538</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>1453.6</v>
+        <v>1451.7</v>
       </c>
       <c r="G20" s="33" t="n">
         <v>20</v>
@@ -14520,7 +14426,7 @@
         <v>8000</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>16908206</v>
+        <v>25506948</v>
       </c>
       <c r="K20" s="9">
         <f>ROUND((E20+G20)*F20+H20+I20,0)</f>
@@ -14538,7 +14444,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>2026.02.11</t>
+          <t>2026.02.27</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -14548,14 +14454,14 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>CPO681</t>
+          <t>CPO685,667</t>
         </is>
       </c>
       <c r="E21" s="33" t="n">
-        <v>26358</v>
+        <v>142189</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>1460.7</v>
+        <v>1441.6</v>
       </c>
       <c r="G21" s="33" t="n">
         <v>20</v>
@@ -14567,7 +14473,7 @@
         <v>8000</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>38550844</v>
+        <v>205028994</v>
       </c>
       <c r="K21" s="9">
         <f>ROUND((E21+G21)*F21+H21+I21,0)</f>
@@ -14585,7 +14491,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>2026.02.19</t>
+          <t>2026.03.06</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -14595,26 +14501,26 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>CPO686,CPO689</t>
+          <t>CPO678-2</t>
         </is>
       </c>
       <c r="E22" s="33" t="n">
-        <v>17538</v>
+        <v>137850</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>1451.7</v>
+        <v>1477.6</v>
       </c>
       <c r="G22" s="33" t="n">
         <v>20</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>10000</v>
+        <v>12500</v>
       </c>
       <c r="I22" s="9" t="n">
         <v>8000</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>25506948</v>
+        <v>203737212</v>
       </c>
       <c r="K22" s="9">
         <f>ROUND((E22+G22)*F22+H22+I22,0)</f>
@@ -14632,7 +14538,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>2026.02.27</t>
+          <t>2026.04.01</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -14642,14 +14548,14 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>CPO685,667</t>
+          <t>CPO690,691</t>
         </is>
       </c>
       <c r="E23" s="33" t="n">
-        <v>142189</v>
+        <v>34354</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>1441.6</v>
+        <v>1505.7</v>
       </c>
       <c r="G23" s="33" t="n">
         <v>20</v>
@@ -14661,7 +14567,7 @@
         <v>8000</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>205028994</v>
+        <v>51777431</v>
       </c>
       <c r="K23" s="9">
         <f>ROUND((E23+G23)*F23+H23+I23,0)</f>
@@ -14679,36 +14585,36 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>2026.03.06</t>
+          <t>2026.04.01</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>CPO678-2</t>
+          <t>GPO469,467,470,471</t>
         </is>
       </c>
       <c r="E24" s="33" t="n">
-        <v>137850</v>
+        <v>6553.05</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>1477.6</v>
+        <v>1506.4</v>
       </c>
       <c r="G24" s="33" t="n">
         <v>20</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>12500</v>
+        <v>10000</v>
       </c>
       <c r="I24" s="9" t="n">
         <v>8000</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>203737212</v>
+        <v>9919642</v>
       </c>
       <c r="K24" s="9">
         <f>ROUND((E24+G24)*F24+H24+I24,0)</f>
@@ -14726,24 +14632,24 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>2026.04.01</t>
+          <t>2026.04.14</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>CPO690,691</t>
+          <t>GPO468-1, 472, 468-2</t>
         </is>
       </c>
       <c r="E25" s="33" t="n">
-        <v>34354</v>
+        <v>57650</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>1505.7</v>
+        <v>1481.9</v>
       </c>
       <c r="G25" s="33" t="n">
         <v>20</v>
@@ -14755,7 +14661,7 @@
         <v>8000</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>51777431</v>
+        <v>85481673</v>
       </c>
       <c r="K25" s="9">
         <f>ROUND((E25+G25)*F25+H25+I25,0)</f>
@@ -14768,94 +14674,94 @@
       <c r="M25" s="115" t="n"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="96" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>2026.04.01</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>GDC</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>GPO469,467,470,471</t>
-        </is>
-      </c>
-      <c r="E26" s="33" t="n">
-        <v>6553.05</v>
-      </c>
-      <c r="F26" s="7" t="n">
-        <v>1506.4</v>
-      </c>
-      <c r="G26" s="33" t="n">
+      <c r="B26" s="96" t="inlineStr">
+        <is>
+          <t>2026.04.21</t>
+        </is>
+      </c>
+      <c r="C26" s="97" t="inlineStr">
+        <is>
+          <t>Ferco</t>
+        </is>
+      </c>
+      <c r="D26" s="96" t="inlineStr">
+        <is>
+          <t>MONOPLEX20260126-01</t>
+        </is>
+      </c>
+      <c r="E26" s="98" t="n">
+        <v>25976</v>
+      </c>
+      <c r="F26" s="196" t="n">
+        <v>1473.3</v>
+      </c>
+      <c r="G26" s="98" t="n">
         <v>20</v>
       </c>
-      <c r="H26" s="9" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I26" s="9" t="n">
+      <c r="H26" s="99" t="n">
+        <v>12500</v>
+      </c>
+      <c r="I26" s="99" t="n">
         <v>8000</v>
       </c>
-      <c r="J26" s="9" t="n">
-        <v>9919642</v>
-      </c>
-      <c r="K26" s="9">
+      <c r="J26" s="99" t="n">
+        <v>38320406</v>
+      </c>
+      <c r="K26" s="99">
         <f>ROUND((E26+G26)*F26+H26+I26,0)</f>
         <v/>
       </c>
-      <c r="L26" s="35">
+      <c r="L26" s="100">
         <f>J26-K26</f>
         <v/>
       </c>
       <c r="M26" s="115" t="n"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="96" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>2026.04.14</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>GDC</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>GPO468-1, 472, 468-2</t>
-        </is>
-      </c>
-      <c r="E27" s="33" t="n">
-        <v>57650</v>
-      </c>
-      <c r="F27" s="7" t="n">
-        <v>1481.9</v>
-      </c>
-      <c r="G27" s="33" t="n">
+      <c r="B27" s="96" t="inlineStr">
+        <is>
+          <t>2026.04.22</t>
+        </is>
+      </c>
+      <c r="C27" s="97" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D27" s="96" t="inlineStr">
+        <is>
+          <t>CPO692(692-1, 692-2)</t>
+        </is>
+      </c>
+      <c r="E27" s="98" t="n">
+        <v>297580</v>
+      </c>
+      <c r="F27" s="196" t="n">
+        <v>1482.8</v>
+      </c>
+      <c r="G27" s="98" t="n">
         <v>20</v>
       </c>
-      <c r="H27" s="9" t="n">
+      <c r="H27" s="99" t="n">
         <v>12500</v>
       </c>
-      <c r="I27" s="9" t="n">
+      <c r="I27" s="99" t="n">
         <v>8000</v>
       </c>
-      <c r="J27" s="9" t="n">
-        <v>85481673</v>
-      </c>
-      <c r="K27" s="9">
+      <c r="J27" s="99" t="n">
+        <v>441301780</v>
+      </c>
+      <c r="K27" s="99">
         <f>ROUND((E27+G27)*F27+H27+I27,0)</f>
         <v/>
       </c>
-      <c r="L27" s="35">
+      <c r="L27" s="100">
         <f>J27-K27</f>
         <v/>
       </c>
@@ -14867,36 +14773,36 @@
       </c>
       <c r="B28" s="96" t="inlineStr">
         <is>
-          <t>2026.04.01</t>
+          <t>2026.04.22</t>
         </is>
       </c>
       <c r="C28" s="97" t="inlineStr">
         <is>
-          <t>Swank</t>
+          <t>MAICO Italia (EUR)</t>
         </is>
       </c>
       <c r="D28" s="96" t="inlineStr">
         <is>
-          <t>(영화 라이센스)</t>
+          <t>EPO18</t>
         </is>
       </c>
       <c r="E28" s="98" t="n">
-        <v>814</v>
+        <v>4388.4</v>
       </c>
       <c r="F28" s="196" t="n">
-        <v>1505</v>
+        <v>1741.08</v>
       </c>
       <c r="G28" s="98" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H28" s="99" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="I28" s="99" t="n">
         <v>8000</v>
       </c>
       <c r="J28" s="99" t="n">
-        <v>1268170</v>
+        <v>7702082</v>
       </c>
       <c r="K28" s="99">
         <f>ROUND((E28+G28)*F28+H28+I28,0)</f>
@@ -14909,192 +14815,190 @@
       <c r="M28" s="115" t="n"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="96" t="n">
+      <c r="A29" s="116" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="96" t="inlineStr">
-        <is>
-          <t>2026.04.02</t>
-        </is>
-      </c>
-      <c r="C29" s="97" t="inlineStr">
-        <is>
-          <t>Monoplex</t>
-        </is>
-      </c>
-      <c r="D29" s="96" t="inlineStr">
-        <is>
-          <t>(영업)</t>
-        </is>
-      </c>
-      <c r="E29" s="98" t="n">
-        <v>30000</v>
-      </c>
-      <c r="F29" s="196" t="n">
-        <v>1520.1</v>
-      </c>
-      <c r="G29" s="98" t="n">
+      <c r="B29" s="116" t="inlineStr">
+        <is>
+          <t>2026.05.04</t>
+        </is>
+      </c>
+      <c r="C29" s="117" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D29" s="116" t="inlineStr">
+        <is>
+          <t>CPO694, CPO695-1, CPO695-2</t>
+        </is>
+      </c>
+      <c r="E29" s="118" t="n">
+        <v>21439</v>
+      </c>
+      <c r="F29" s="197" t="n">
+        <v>1474.9</v>
+      </c>
+      <c r="G29" s="118" t="n">
         <v>20</v>
       </c>
-      <c r="H29" s="99" t="n">
-        <v>25000</v>
-      </c>
-      <c r="I29" s="99" t="n">
+      <c r="H29" s="120" t="n">
+        <v>12500</v>
+      </c>
+      <c r="I29" s="120" t="n">
         <v>8000</v>
       </c>
-      <c r="J29" s="99" t="n">
-        <v>45666402</v>
-      </c>
-      <c r="K29" s="99">
+      <c r="J29" s="120" t="n">
+        <v>31670379</v>
+      </c>
+      <c r="K29" s="120">
         <f>ROUND((E29+G29)*F29+H29+I29,0)</f>
         <v/>
       </c>
-      <c r="L29" s="100">
+      <c r="L29" s="121">
         <f>J29-K29</f>
         <v/>
       </c>
-      <c r="M29" s="115" t="n"/>
+      <c r="M29" s="114" t="n"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="96" t="n">
+      <c r="A30" s="116" t="n">
         <v>28</v>
       </c>
-      <c r="B30" s="96" t="inlineStr">
-        <is>
-          <t>2026.04.21</t>
-        </is>
-      </c>
-      <c r="C30" s="97" t="inlineStr">
+      <c r="B30" s="116" t="inlineStr">
+        <is>
+          <t>2026.05.04</t>
+        </is>
+      </c>
+      <c r="C30" s="117" t="inlineStr">
+        <is>
+          <t>Integ Process Group</t>
+        </is>
+      </c>
+      <c r="D30" s="116" t="inlineStr">
+        <is>
+          <t>IPO016 (JNR-410)</t>
+        </is>
+      </c>
+      <c r="E30" s="118" t="n">
+        <v>6800</v>
+      </c>
+      <c r="F30" s="197" t="n">
+        <v>1475.2</v>
+      </c>
+      <c r="G30" s="118" t="n">
+        <v>20</v>
+      </c>
+      <c r="H30" s="120" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I30" s="120" t="n">
+        <v>8000</v>
+      </c>
+      <c r="J30" s="120" t="n">
+        <v>10078864</v>
+      </c>
+      <c r="K30" s="120">
+        <f>ROUND((E30+G30)*F30+H30+I30,0)</f>
+        <v/>
+      </c>
+      <c r="L30" s="121">
+        <f>J30-K30</f>
+        <v/>
+      </c>
+      <c r="M30" s="114" t="n"/>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="116" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="116" t="inlineStr">
+        <is>
+          <t>2026.05.12</t>
+        </is>
+      </c>
+      <c r="C31" s="117" t="inlineStr">
         <is>
           <t>Ferco</t>
         </is>
       </c>
-      <c r="D30" s="96" t="inlineStr">
-        <is>
-          <t>MONOPLEX20260126-01</t>
-        </is>
-      </c>
-      <c r="E30" s="98" t="n">
-        <v>25976</v>
-      </c>
-      <c r="F30" s="196" t="n">
-        <v>1473.3</v>
-      </c>
-      <c r="G30" s="98" t="n">
+      <c r="D31" s="116" t="inlineStr">
+        <is>
+          <t>PI44133-1</t>
+        </is>
+      </c>
+      <c r="E31" s="118" t="n">
+        <v>4416</v>
+      </c>
+      <c r="F31" s="197" t="n">
+        <v>1755.24</v>
+      </c>
+      <c r="G31" s="118" t="n">
+        <v>25</v>
+      </c>
+      <c r="H31" s="120" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I31" s="120" t="n">
+        <v>8000</v>
+      </c>
+      <c r="J31" s="120" t="n">
+        <v>7813020</v>
+      </c>
+      <c r="K31" s="120">
+        <f>ROUND((E31+G31)*F31+H31+I31,0)</f>
+        <v/>
+      </c>
+      <c r="L31" s="121">
+        <f>J31-K31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="116" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="116" t="inlineStr">
+        <is>
+          <t>2026.05.19</t>
+        </is>
+      </c>
+      <c r="C32" s="117" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D32" s="116" t="inlineStr">
+        <is>
+          <t>GPO478</t>
+        </is>
+      </c>
+      <c r="E32" s="118" t="n">
+        <v>180</v>
+      </c>
+      <c r="F32" s="197" t="n">
+        <v>1518.9</v>
+      </c>
+      <c r="G32" s="118" t="n">
         <v>20</v>
       </c>
-      <c r="H30" s="99" t="n">
-        <v>12500</v>
-      </c>
-      <c r="I30" s="99" t="n">
+      <c r="H32" s="120" t="n">
+        <v>2500</v>
+      </c>
+      <c r="I32" s="120" t="n">
         <v>8000</v>
       </c>
-      <c r="J30" s="99" t="n">
-        <v>38320406</v>
-      </c>
-      <c r="K30" s="99">
-        <f>ROUND((E30+G30)*F30+H30+I30,0)</f>
-        <v/>
-      </c>
-      <c r="L30" s="100">
-        <f>J30-K30</f>
-        <v/>
-      </c>
-      <c r="M30" s="115" t="n"/>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="96" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" s="96" t="inlineStr">
-        <is>
-          <t>2026.04.22</t>
-        </is>
-      </c>
-      <c r="C31" s="97" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D31" s="96" t="inlineStr">
-        <is>
-          <t>CPO692(692-1, 692-2)</t>
-        </is>
-      </c>
-      <c r="E31" s="98" t="n">
-        <v>297580</v>
-      </c>
-      <c r="F31" s="196" t="n">
-        <v>1482.8</v>
-      </c>
-      <c r="G31" s="98" t="n">
-        <v>20</v>
-      </c>
-      <c r="H31" s="99" t="n">
-        <v>12500</v>
-      </c>
-      <c r="I31" s="99" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J31" s="99" t="n">
-        <v>441301780</v>
-      </c>
-      <c r="K31" s="99">
-        <f>ROUND((E31+G31)*F31+H31+I31,0)</f>
-        <v/>
-      </c>
-      <c r="L31" s="100">
-        <f>J31-K31</f>
-        <v/>
-      </c>
-      <c r="M31" s="115" t="n"/>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="96" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" s="96" t="inlineStr">
-        <is>
-          <t>2026.04.22</t>
-        </is>
-      </c>
-      <c r="C32" s="97" t="inlineStr">
-        <is>
-          <t>MAICO Italia (EUR)</t>
-        </is>
-      </c>
-      <c r="D32" s="96" t="inlineStr">
-        <is>
-          <t>EPO18</t>
-        </is>
-      </c>
-      <c r="E32" s="98" t="n">
-        <v>4388.4</v>
-      </c>
-      <c r="F32" s="196" t="n">
-        <v>1741.08</v>
-      </c>
-      <c r="G32" s="98" t="n">
-        <v>25</v>
-      </c>
-      <c r="H32" s="99" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I32" s="99" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J32" s="99" t="n">
-        <v>7702082</v>
-      </c>
-      <c r="K32" s="99">
+      <c r="J32" s="120" t="n">
+        <v>314280</v>
+      </c>
+      <c r="K32" s="120">
         <f>ROUND((E32+G32)*F32+H32+I32,0)</f>
         <v/>
       </c>
-      <c r="L32" s="100">
+      <c r="L32" s="121">
         <f>J32-K32</f>
         <v/>
       </c>
-      <c r="M32" s="115" t="n"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="116" t="n">
@@ -15102,7 +15006,7 @@
       </c>
       <c r="B33" s="116" t="inlineStr">
         <is>
-          <t>2026.05.04</t>
+          <t>2026.05.20</t>
         </is>
       </c>
       <c r="C33" s="117" t="inlineStr">
@@ -15112,26 +15016,26 @@
       </c>
       <c r="D33" s="116" t="inlineStr">
         <is>
-          <t>CPO694, CPO695-1, CPO695-2</t>
+          <t>CPO698</t>
         </is>
       </c>
       <c r="E33" s="118" t="n">
-        <v>21439</v>
+        <v>4290</v>
       </c>
       <c r="F33" s="197" t="n">
-        <v>1474.9</v>
+        <v>1510.6</v>
       </c>
       <c r="G33" s="118" t="n">
         <v>20</v>
       </c>
       <c r="H33" s="120" t="n">
-        <v>12500</v>
+        <v>7500</v>
       </c>
       <c r="I33" s="120" t="n">
         <v>8000</v>
       </c>
       <c r="J33" s="120" t="n">
-        <v>31670379</v>
+        <v>6526186</v>
       </c>
       <c r="K33" s="120">
         <f>ROUND((E33+G33)*F33+H33+I33,0)</f>
@@ -15141,7 +15045,6 @@
         <f>J33-K33</f>
         <v/>
       </c>
-      <c r="M33" s="114" t="n"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="116" t="n">
@@ -15149,36 +15052,36 @@
       </c>
       <c r="B34" s="116" t="inlineStr">
         <is>
-          <t>2026.05.04</t>
+          <t>2026.05.29</t>
         </is>
       </c>
       <c r="C34" s="117" t="inlineStr">
         <is>
-          <t>Integ Process Group</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D34" s="116" t="inlineStr">
         <is>
-          <t>IPO016 (JNR-410)</t>
+          <t>GPO480, GPO479, GPO473-1</t>
         </is>
       </c>
       <c r="E34" s="118" t="n">
-        <v>6800</v>
+        <v>99140</v>
       </c>
       <c r="F34" s="197" t="n">
-        <v>1475.2</v>
+        <v>1502.8</v>
       </c>
       <c r="G34" s="118" t="n">
         <v>20</v>
       </c>
       <c r="H34" s="120" t="n">
-        <v>10000</v>
+        <v>12500</v>
       </c>
       <c r="I34" s="120" t="n">
         <v>8000</v>
       </c>
       <c r="J34" s="120" t="n">
-        <v>10078864</v>
+        <v>149038148</v>
       </c>
       <c r="K34" s="120">
         <f>ROUND((E34+G34)*F34+H34+I34,0)</f>
@@ -15188,7 +15091,6 @@
         <f>J34-K34</f>
         <v/>
       </c>
-      <c r="M34" s="114" t="n"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="116" t="n">
@@ -15196,36 +15098,36 @@
       </c>
       <c r="B35" s="116" t="inlineStr">
         <is>
-          <t>2026.05.12</t>
+          <t>2026.05.29</t>
         </is>
       </c>
       <c r="C35" s="117" t="inlineStr">
         <is>
-          <t>Ferco</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D35" s="116" t="inlineStr">
         <is>
-          <t>PI44133-1</t>
+          <t>CPO697, CPO696-1, CPO696-2</t>
         </is>
       </c>
       <c r="E35" s="118" t="n">
-        <v>4416</v>
+        <v>101638</v>
       </c>
       <c r="F35" s="197" t="n">
-        <v>1755.24</v>
+        <v>1502.7</v>
       </c>
       <c r="G35" s="118" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H35" s="120" t="n">
-        <v>10000</v>
+        <v>12500</v>
       </c>
       <c r="I35" s="120" t="n">
         <v>8000</v>
       </c>
       <c r="J35" s="120" t="n">
-        <v>7813020</v>
+        <v>152781976</v>
       </c>
       <c r="K35" s="120">
         <f>ROUND((E35+G35)*F35+H35+I35,0)</f>
@@ -15237,185 +15139,185 @@
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="116" t="n">
+      <c r="A36" s="234" t="n">
         <v>34</v>
       </c>
-      <c r="B36" s="116" t="inlineStr">
-        <is>
-          <t>2026.05.19</t>
-        </is>
-      </c>
-      <c r="C36" s="117" t="inlineStr">
+      <c r="B36" s="234" t="inlineStr">
+        <is>
+          <t>2026.06.10</t>
+        </is>
+      </c>
+      <c r="C36" s="235" t="inlineStr">
         <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D36" s="116" t="inlineStr">
-        <is>
-          <t>GPO478</t>
-        </is>
-      </c>
-      <c r="E36" s="118" t="n">
-        <v>180</v>
-      </c>
-      <c r="F36" s="197" t="n">
-        <v>1518.9</v>
-      </c>
-      <c r="G36" s="118" t="n">
+      <c r="D36" s="234" t="inlineStr">
+        <is>
+          <t>GPO481, GPO473-2, GPO473-3</t>
+        </is>
+      </c>
+      <c r="E36" s="236" t="n">
+        <v>119060</v>
+      </c>
+      <c r="F36" s="237" t="n">
+        <v>1525.3</v>
+      </c>
+      <c r="G36" s="236" t="n">
         <v>20</v>
       </c>
-      <c r="H36" s="120" t="n">
-        <v>2500</v>
-      </c>
-      <c r="I36" s="120" t="n">
+      <c r="H36" s="238" t="n">
+        <v>12500</v>
+      </c>
+      <c r="I36" s="238" t="n">
         <v>8000</v>
       </c>
-      <c r="J36" s="120" t="n">
-        <v>314280</v>
-      </c>
-      <c r="K36" s="120">
+      <c r="J36" s="238" t="n">
+        <v>181653224</v>
+      </c>
+      <c r="K36" s="238">
         <f>ROUND((E36+G36)*F36+H36+I36,0)</f>
         <v/>
       </c>
-      <c r="L36" s="121">
+      <c r="L36" s="239">
         <f>J36-K36</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="116" t="n">
+      <c r="A37" s="234" t="n">
         <v>35</v>
       </c>
-      <c r="B37" s="116" t="inlineStr">
-        <is>
-          <t>2026.05.20</t>
-        </is>
-      </c>
-      <c r="C37" s="117" t="inlineStr">
+      <c r="B37" s="234" t="inlineStr">
+        <is>
+          <t>2026.06.17</t>
+        </is>
+      </c>
+      <c r="C37" s="235" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D37" s="116" t="inlineStr">
-        <is>
-          <t>CPO698</t>
-        </is>
-      </c>
-      <c r="E37" s="118" t="n">
-        <v>4290</v>
-      </c>
-      <c r="F37" s="197" t="n">
-        <v>1510.6</v>
-      </c>
-      <c r="G37" s="118" t="n">
+      <c r="D37" s="234" t="inlineStr">
+        <is>
+          <t>CPO696-3</t>
+        </is>
+      </c>
+      <c r="E37" s="236" t="n">
+        <v>351274</v>
+      </c>
+      <c r="F37" s="237" t="n">
+        <v>1518</v>
+      </c>
+      <c r="G37" s="236" t="n">
         <v>20</v>
       </c>
-      <c r="H37" s="120" t="n">
-        <v>7500</v>
-      </c>
-      <c r="I37" s="120" t="n">
+      <c r="H37" s="238" t="n">
+        <v>12500</v>
+      </c>
+      <c r="I37" s="238" t="n">
         <v>8000</v>
       </c>
-      <c r="J37" s="120" t="n">
-        <v>6526186</v>
-      </c>
-      <c r="K37" s="120">
+      <c r="J37" s="238" t="n">
+        <v>533284792</v>
+      </c>
+      <c r="K37" s="238">
         <f>ROUND((E37+G37)*F37+H37+I37,0)</f>
         <v/>
       </c>
-      <c r="L37" s="121">
+      <c r="L37" s="239">
         <f>J37-K37</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="116" t="n">
+      <c r="A38" s="234" t="n">
         <v>36</v>
       </c>
-      <c r="B38" s="116" t="inlineStr">
-        <is>
-          <t>2026.05.29</t>
-        </is>
-      </c>
-      <c r="C38" s="117" t="inlineStr">
-        <is>
-          <t>GDC</t>
-        </is>
-      </c>
-      <c r="D38" s="116" t="inlineStr">
-        <is>
-          <t>GPO480, GPO479, GPO473-1</t>
-        </is>
-      </c>
-      <c r="E38" s="118" t="n">
-        <v>99140</v>
-      </c>
-      <c r="F38" s="197" t="n">
-        <v>1502.8</v>
-      </c>
-      <c r="G38" s="118" t="n">
+      <c r="B38" s="234" t="inlineStr">
+        <is>
+          <t>2026.06.17</t>
+        </is>
+      </c>
+      <c r="C38" s="235" t="inlineStr">
+        <is>
+          <t>Appotronics</t>
+        </is>
+      </c>
+      <c r="D38" s="234" t="inlineStr">
+        <is>
+          <t>APO001 (S20-C2220-BEAB)</t>
+        </is>
+      </c>
+      <c r="E38" s="236" t="n">
+        <v>12400</v>
+      </c>
+      <c r="F38" s="237" t="n">
+        <v>1517.1</v>
+      </c>
+      <c r="G38" s="236" t="n">
         <v>20</v>
       </c>
-      <c r="H38" s="120" t="n">
+      <c r="H38" s="238" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I38" s="238" t="n">
+        <v>8000</v>
+      </c>
+      <c r="J38" s="238" t="n">
+        <v>18860382</v>
+      </c>
+      <c r="K38" s="238">
+        <f>ROUND((E38+G38)*F38+H38+I38,0)</f>
+        <v/>
+      </c>
+      <c r="L38" s="239">
+        <f>J38-K38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="A39" s="234" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="234" t="inlineStr">
+        <is>
+          <t>2026.06.17</t>
+        </is>
+      </c>
+      <c r="C39" s="235" t="inlineStr">
+        <is>
+          <t>MMK Europe</t>
+        </is>
+      </c>
+      <c r="D39" s="234" t="inlineStr">
+        <is>
+          <t>MPO67, MPO68</t>
+        </is>
+      </c>
+      <c r="E39" s="236" t="n">
+        <v>60726</v>
+      </c>
+      <c r="F39" s="237" t="n">
+        <v>1517.3</v>
+      </c>
+      <c r="G39" s="236" t="n">
+        <v>20</v>
+      </c>
+      <c r="H39" s="238" t="n">
         <v>12500</v>
       </c>
-      <c r="I38" s="120" t="n">
+      <c r="I39" s="238" t="n">
         <v>8000</v>
       </c>
-      <c r="J38" s="120" t="n">
-        <v>149038148</v>
-      </c>
-      <c r="K38" s="120">
-        <f>ROUND((E38+G38)*F38+H38+I38,0)</f>
-        <v/>
-      </c>
-      <c r="L38" s="121">
-        <f>J38-K38</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="116" t="n">
-        <v>37</v>
-      </c>
-      <c r="B39" s="116" t="inlineStr">
-        <is>
-          <t>2026.05.29</t>
-        </is>
-      </c>
-      <c r="C39" s="117" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D39" s="116" t="inlineStr">
-        <is>
-          <t>CPO697, CPO696-1, CPO696-2</t>
-        </is>
-      </c>
-      <c r="E39" s="118" t="n">
-        <v>101638</v>
-      </c>
-      <c r="F39" s="197" t="n">
-        <v>1502.7</v>
-      </c>
-      <c r="G39" s="118" t="n">
-        <v>20</v>
-      </c>
-      <c r="H39" s="120" t="n">
-        <v>12500</v>
-      </c>
-      <c r="I39" s="120" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J39" s="120" t="n">
-        <v>152781976</v>
-      </c>
-      <c r="K39" s="120">
+      <c r="J39" s="238" t="n">
+        <v>92190405</v>
+      </c>
+      <c r="K39" s="238">
         <f>ROUND((E39+G39)*F39+H39+I39,0)</f>
         <v/>
       </c>
-      <c r="L39" s="121">
+      <c r="L39" s="239">
         <f>J39-K39</f>
         <v/>
       </c>
@@ -15426,7 +15328,7 @@
       </c>
       <c r="B40" s="234" t="inlineStr">
         <is>
-          <t>2026.06.10</t>
+          <t>2026.06.17</t>
         </is>
       </c>
       <c r="C40" s="235" t="inlineStr">
@@ -15436,26 +15338,26 @@
       </c>
       <c r="D40" s="234" t="inlineStr">
         <is>
-          <t>GPO481, GPO473-2, GPO473-3</t>
+          <t>GPO475, SR-1000수리</t>
         </is>
       </c>
       <c r="E40" s="236" t="n">
-        <v>119060</v>
+        <v>2040</v>
       </c>
       <c r="F40" s="237" t="n">
-        <v>1525.3</v>
+        <v>1516.8</v>
       </c>
       <c r="G40" s="236" t="n">
         <v>20</v>
       </c>
       <c r="H40" s="238" t="n">
-        <v>12500</v>
+        <v>7500</v>
       </c>
       <c r="I40" s="238" t="n">
         <v>8000</v>
       </c>
       <c r="J40" s="238" t="n">
-        <v>181653224</v>
+        <v>3140108</v>
       </c>
       <c r="K40" s="238">
         <f>ROUND((E40+G40)*F40+H40+I40,0)</f>
@@ -15467,325 +15369,321 @@
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="234" t="n">
-        <v>39</v>
-      </c>
-      <c r="B41" s="234" t="inlineStr">
-        <is>
-          <t>2026.06.17</t>
-        </is>
-      </c>
-      <c r="C41" s="235" t="inlineStr">
+      <c r="A41" s="169" t="inlineStr">
+        <is>
+          <t>② PO별 비용 안분 내역</t>
+        </is>
+      </c>
+      <c r="B41" s="148" t="n"/>
+      <c r="C41" s="148" t="n"/>
+      <c r="D41" s="148" t="n"/>
+      <c r="E41" s="148" t="n"/>
+      <c r="F41" s="148" t="n"/>
+      <c r="G41" s="148" t="n"/>
+      <c r="H41" s="148" t="n"/>
+      <c r="I41" s="148" t="n"/>
+      <c r="J41" s="148" t="n"/>
+      <c r="K41" s="148" t="n"/>
+      <c r="L41" s="149" t="n"/>
+      <c r="M41" s="115" t="n"/>
+    </row>
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="A42" s="150" t="inlineStr">
+        <is>
+          <t>PO No.</t>
+        </is>
+      </c>
+      <c r="B42" s="150" t="inlineStr">
+        <is>
+          <t>송금일</t>
+        </is>
+      </c>
+      <c r="C42" s="150" t="inlineStr">
+        <is>
+          <t>업체</t>
+        </is>
+      </c>
+      <c r="D42" s="150" t="inlineStr">
+        <is>
+          <t>PO USD</t>
+        </is>
+      </c>
+      <c r="E42" s="150" t="inlineStr">
+        <is>
+          <t>그룹총USD</t>
+        </is>
+      </c>
+      <c r="F42" s="150" t="inlineStr">
+        <is>
+          <t>배부비율</t>
+        </is>
+      </c>
+      <c r="G42" s="150" t="inlineStr">
+        <is>
+          <t>적용환율</t>
+        </is>
+      </c>
+      <c r="H42" s="150" t="inlineStr">
+        <is>
+          <t>원화환산액</t>
+        </is>
+      </c>
+      <c r="I42" s="150" t="inlineStr">
+        <is>
+          <t>중개수수료안분</t>
+        </is>
+      </c>
+      <c r="J42" s="150" t="inlineStr">
+        <is>
+          <t>수수료안분</t>
+        </is>
+      </c>
+      <c r="K42" s="150" t="inlineStr">
+        <is>
+          <t>전신료안분</t>
+        </is>
+      </c>
+      <c r="L42" s="150" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="M42" s="115" t="n"/>
+    </row>
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="A43" s="116" t="inlineStr">
+        <is>
+          <t>CPO678-1</t>
+        </is>
+      </c>
+      <c r="B43" s="116" t="inlineStr">
+        <is>
+          <t>2025.12.16</t>
+        </is>
+      </c>
+      <c r="C43" s="117" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D41" s="234" t="inlineStr">
-        <is>
-          <t>CPO696-3</t>
-        </is>
-      </c>
-      <c r="E41" s="236" t="n">
-        <v>351274</v>
-      </c>
-      <c r="F41" s="237" t="n">
-        <v>1518</v>
-      </c>
-      <c r="G41" s="236" t="n">
-        <v>20</v>
-      </c>
-      <c r="H41" s="238" t="n">
-        <v>12500</v>
-      </c>
-      <c r="I41" s="238" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J41" s="238" t="n">
-        <v>533284792</v>
-      </c>
-      <c r="K41" s="238">
-        <f>ROUND((E41+G41)*F41+H41+I41,0)</f>
-        <v/>
-      </c>
-      <c r="L41" s="239">
-        <f>J41-K41</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="234" t="n">
-        <v>40</v>
-      </c>
-      <c r="B42" s="234" t="inlineStr">
-        <is>
-          <t>2026.06.17</t>
-        </is>
-      </c>
-      <c r="C42" s="235" t="inlineStr">
-        <is>
-          <t>Appotronics</t>
-        </is>
-      </c>
-      <c r="D42" s="234" t="inlineStr">
-        <is>
-          <t>APO001 (S20-C2220-BEAB)</t>
-        </is>
-      </c>
-      <c r="E42" s="236" t="n">
-        <v>12400</v>
-      </c>
-      <c r="F42" s="237" t="n">
-        <v>1517.1</v>
-      </c>
-      <c r="G42" s="236" t="n">
-        <v>20</v>
-      </c>
-      <c r="H42" s="238" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I42" s="238" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J42" s="238" t="n">
-        <v>18860382</v>
-      </c>
-      <c r="K42" s="238">
-        <f>ROUND((E42+G42)*F42+H42+I42,0)</f>
-        <v/>
-      </c>
-      <c r="L42" s="239">
-        <f>J42-K42</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="234" t="n">
-        <v>41</v>
-      </c>
-      <c r="B43" s="234" t="inlineStr">
-        <is>
-          <t>2026.06.17</t>
-        </is>
-      </c>
-      <c r="C43" s="235" t="inlineStr">
-        <is>
-          <t>MMK Europe</t>
-        </is>
-      </c>
-      <c r="D43" s="234" t="inlineStr">
-        <is>
-          <t>MPO67, MPO68</t>
-        </is>
-      </c>
-      <c r="E43" s="236" t="n">
-        <v>60726</v>
-      </c>
-      <c r="F43" s="237" t="n">
-        <v>1517.3</v>
-      </c>
-      <c r="G43" s="236" t="n">
-        <v>20</v>
-      </c>
-      <c r="H43" s="238" t="n">
-        <v>12500</v>
-      </c>
-      <c r="I43" s="238" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J43" s="238" t="n">
-        <v>92190405</v>
-      </c>
-      <c r="K43" s="238">
-        <f>ROUND((E43+G43)*F43+H43+I43,0)</f>
-        <v/>
-      </c>
-      <c r="L43" s="239">
-        <f>J43-K43</f>
-        <v/>
-      </c>
+      <c r="D43" s="118" t="n">
+        <v>139083</v>
+      </c>
+      <c r="E43" s="118" t="n">
+        <v>143557</v>
+      </c>
+      <c r="F43" s="122" t="n">
+        <v>0.968835</v>
+      </c>
+      <c r="G43" s="118" t="n">
+        <v>1479.7</v>
+      </c>
+      <c r="H43" s="120" t="n">
+        <v>205801115</v>
+      </c>
+      <c r="I43" s="120" t="n">
+        <v>28672</v>
+      </c>
+      <c r="J43" s="120" t="n">
+        <v>12110</v>
+      </c>
+      <c r="K43" s="120" t="n">
+        <v>7751</v>
+      </c>
+      <c r="L43" s="121" t="n">
+        <v>205849648</v>
+      </c>
+      <c r="M43" s="115" t="n"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="234" t="n">
-        <v>42</v>
-      </c>
-      <c r="B44" s="234" t="inlineStr">
-        <is>
-          <t>2026.06.17</t>
-        </is>
-      </c>
-      <c r="C44" s="235" t="inlineStr">
+      <c r="A44" s="116" t="inlineStr">
+        <is>
+          <t>CPO679</t>
+        </is>
+      </c>
+      <c r="B44" s="116" t="inlineStr">
+        <is>
+          <t>2025.12.16</t>
+        </is>
+      </c>
+      <c r="C44" s="117" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D44" s="118" t="n">
+        <v>4474</v>
+      </c>
+      <c r="E44" s="118" t="n">
+        <v>143557</v>
+      </c>
+      <c r="F44" s="122" t="n">
+        <v>0.031165</v>
+      </c>
+      <c r="G44" s="118" t="n">
+        <v>1479.7</v>
+      </c>
+      <c r="H44" s="120" t="n">
+        <v>6620178</v>
+      </c>
+      <c r="I44" s="120" t="n">
+        <v>922</v>
+      </c>
+      <c r="J44" s="120" t="n">
+        <v>390</v>
+      </c>
+      <c r="K44" s="120" t="n">
+        <v>249</v>
+      </c>
+      <c r="L44" s="121" t="n">
+        <v>6621739</v>
+      </c>
+      <c r="M44" s="115" t="n"/>
+    </row>
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="A45" s="116" t="inlineStr">
+        <is>
+          <t>MPO65</t>
+        </is>
+      </c>
+      <c r="B45" s="116" t="inlineStr">
+        <is>
+          <t>2025.12.16</t>
+        </is>
+      </c>
+      <c r="C45" s="117" t="inlineStr">
+        <is>
+          <t>MAG</t>
+        </is>
+      </c>
+      <c r="D45" s="118" t="n">
+        <v>4936</v>
+      </c>
+      <c r="E45" s="118" t="n">
+        <v>15040</v>
+      </c>
+      <c r="F45" s="122" t="n">
+        <v>0.328191</v>
+      </c>
+      <c r="G45" s="118" t="n">
+        <v>1480</v>
+      </c>
+      <c r="H45" s="120" t="n">
+        <v>7305280</v>
+      </c>
+      <c r="I45" s="120" t="n">
+        <v>9714</v>
+      </c>
+      <c r="J45" s="120" t="n">
+        <v>3282</v>
+      </c>
+      <c r="K45" s="120" t="n">
+        <v>2626</v>
+      </c>
+      <c r="L45" s="121" t="n">
+        <v>7320902</v>
+      </c>
+      <c r="M45" s="115" t="n"/>
+    </row>
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="A46" s="116" t="inlineStr">
+        <is>
+          <t>GPO451</t>
+        </is>
+      </c>
+      <c r="B46" s="116" t="inlineStr">
+        <is>
+          <t>2025.12.29</t>
+        </is>
+      </c>
+      <c r="C46" s="117" t="inlineStr">
         <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D44" s="234" t="inlineStr">
-        <is>
-          <t>GPO475, SR-1000수리</t>
-        </is>
-      </c>
-      <c r="E44" s="236" t="n">
-        <v>2040</v>
-      </c>
-      <c r="F44" s="237" t="n">
-        <v>1516.8</v>
-      </c>
-      <c r="G44" s="236" t="n">
-        <v>20</v>
-      </c>
-      <c r="H44" s="238" t="n">
-        <v>7500</v>
-      </c>
-      <c r="I44" s="238" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J44" s="238" t="n">
-        <v>3140108</v>
-      </c>
-      <c r="K44" s="238">
-        <f>ROUND((E44+G44)*F44+H44+I44,0)</f>
-        <v/>
-      </c>
-      <c r="L44" s="239">
-        <f>J44-K44</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="169" t="inlineStr">
-        <is>
-          <t>② PO별 비용 안분 내역</t>
-        </is>
-      </c>
-      <c r="B45" s="148" t="n"/>
-      <c r="C45" s="148" t="n"/>
-      <c r="D45" s="148" t="n"/>
-      <c r="E45" s="148" t="n"/>
-      <c r="F45" s="148" t="n"/>
-      <c r="G45" s="148" t="n"/>
-      <c r="H45" s="148" t="n"/>
-      <c r="I45" s="148" t="n"/>
-      <c r="J45" s="148" t="n"/>
-      <c r="K45" s="148" t="n"/>
-      <c r="L45" s="149" t="n"/>
-      <c r="M45" s="115" t="n"/>
-    </row>
-    <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="150" t="inlineStr">
-        <is>
-          <t>PO No.</t>
-        </is>
-      </c>
-      <c r="B46" s="150" t="inlineStr">
-        <is>
-          <t>송금일</t>
-        </is>
-      </c>
-      <c r="C46" s="150" t="inlineStr">
-        <is>
-          <t>업체</t>
-        </is>
-      </c>
-      <c r="D46" s="150" t="inlineStr">
-        <is>
-          <t>PO USD</t>
-        </is>
-      </c>
-      <c r="E46" s="150" t="inlineStr">
-        <is>
-          <t>그룹총USD</t>
-        </is>
-      </c>
-      <c r="F46" s="150" t="inlineStr">
-        <is>
-          <t>배부비율</t>
-        </is>
-      </c>
-      <c r="G46" s="150" t="inlineStr">
-        <is>
-          <t>적용환율</t>
-        </is>
-      </c>
-      <c r="H46" s="150" t="inlineStr">
-        <is>
-          <t>원화환산액</t>
-        </is>
-      </c>
-      <c r="I46" s="150" t="inlineStr">
-        <is>
-          <t>중개수수료안분</t>
-        </is>
-      </c>
-      <c r="J46" s="150" t="inlineStr">
-        <is>
-          <t>수수료안분</t>
-        </is>
-      </c>
-      <c r="K46" s="150" t="inlineStr">
-        <is>
-          <t>전신료안분</t>
-        </is>
-      </c>
-      <c r="L46" s="150" t="inlineStr">
-        <is>
-          <t>합계</t>
-        </is>
+      <c r="D46" s="118" t="n">
+        <v>9060</v>
+      </c>
+      <c r="E46" s="118" t="n">
+        <v>13860</v>
+      </c>
+      <c r="F46" s="122" t="n">
+        <v>0.65368</v>
+      </c>
+      <c r="G46" s="118" t="n">
+        <v>1439.1</v>
+      </c>
+      <c r="H46" s="120" t="n">
+        <v>13038246</v>
+      </c>
+      <c r="I46" s="120" t="n">
+        <v>18814</v>
+      </c>
+      <c r="J46" s="120" t="n">
+        <v>6537</v>
+      </c>
+      <c r="K46" s="120" t="n">
+        <v>5229</v>
+      </c>
+      <c r="L46" s="121" t="n">
+        <v>13068826</v>
       </c>
       <c r="M46" s="115" t="n"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="116" t="inlineStr">
         <is>
-          <t>CPO678-1</t>
+          <t>GPO458</t>
         </is>
       </c>
       <c r="B47" s="116" t="inlineStr">
         <is>
-          <t>2025.12.16</t>
+          <t>2025.12.29</t>
         </is>
       </c>
       <c r="C47" s="117" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D47" s="118" t="n">
-        <v>139083</v>
+        <v>350</v>
       </c>
       <c r="E47" s="118" t="n">
-        <v>143557</v>
+        <v>13860</v>
       </c>
       <c r="F47" s="122" t="n">
-        <v>0.968835</v>
+        <v>0.025253</v>
       </c>
       <c r="G47" s="118" t="n">
-        <v>1479.7</v>
+        <v>1439.1</v>
       </c>
       <c r="H47" s="120" t="n">
-        <v>205801115</v>
+        <v>503685</v>
       </c>
       <c r="I47" s="120" t="n">
-        <v>28672</v>
+        <v>727</v>
       </c>
       <c r="J47" s="120" t="n">
-        <v>12110</v>
+        <v>253</v>
       </c>
       <c r="K47" s="120" t="n">
-        <v>7751</v>
+        <v>202</v>
       </c>
       <c r="L47" s="121" t="n">
-        <v>205849648</v>
+        <v>504867</v>
       </c>
       <c r="M47" s="115" t="n"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="116" t="inlineStr">
         <is>
-          <t>CPO679</t>
+          <t>CPO680</t>
         </is>
       </c>
       <c r="B48" s="116" t="inlineStr">
         <is>
-          <t>2025.12.16</t>
+          <t>2026.01.13</t>
         </is>
       </c>
       <c r="C48" s="117" t="inlineStr">
@@ -15794,88 +15692,88 @@
         </is>
       </c>
       <c r="D48" s="118" t="n">
-        <v>4474</v>
+        <v>252</v>
       </c>
       <c r="E48" s="118" t="n">
-        <v>143557</v>
+        <v>252</v>
       </c>
       <c r="F48" s="122" t="n">
-        <v>0.031165</v>
+        <v>1</v>
       </c>
       <c r="G48" s="118" t="n">
-        <v>1479.7</v>
+        <v>1479</v>
       </c>
       <c r="H48" s="120" t="n">
-        <v>6620178</v>
+        <v>372708</v>
       </c>
       <c r="I48" s="120" t="n">
-        <v>922</v>
+        <v>29580</v>
       </c>
       <c r="J48" s="120" t="n">
-        <v>390</v>
+        <v>2500</v>
       </c>
       <c r="K48" s="120" t="n">
-        <v>249</v>
+        <v>8000</v>
       </c>
       <c r="L48" s="121" t="n">
-        <v>6621739</v>
+        <v>412788</v>
       </c>
       <c r="M48" s="115" t="n"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="116" t="inlineStr">
         <is>
-          <t>MPO65</t>
+          <t>GPO459</t>
         </is>
       </c>
       <c r="B49" s="116" t="inlineStr">
         <is>
-          <t>2025.12.16</t>
+          <t>2026.01.21</t>
         </is>
       </c>
       <c r="C49" s="117" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D49" s="118" t="n">
-        <v>4936</v>
+        <v>450</v>
       </c>
       <c r="E49" s="118" t="n">
-        <v>15040</v>
+        <v>3700</v>
       </c>
       <c r="F49" s="122" t="n">
-        <v>0.328191</v>
+        <v>0.121622</v>
       </c>
       <c r="G49" s="118" t="n">
-        <v>1480</v>
+        <v>1475.7</v>
       </c>
       <c r="H49" s="120" t="n">
-        <v>7305280</v>
+        <v>664065</v>
       </c>
       <c r="I49" s="120" t="n">
-        <v>9714</v>
+        <v>3590</v>
       </c>
       <c r="J49" s="120" t="n">
-        <v>3282</v>
+        <v>912</v>
       </c>
       <c r="K49" s="120" t="n">
-        <v>2626</v>
+        <v>973</v>
       </c>
       <c r="L49" s="121" t="n">
-        <v>7320902</v>
+        <v>669540</v>
       </c>
       <c r="M49" s="115" t="n"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="116" t="inlineStr">
         <is>
-          <t>GPO451</t>
+          <t>GPO460</t>
         </is>
       </c>
       <c r="B50" s="116" t="inlineStr">
         <is>
-          <t>2025.12.29</t>
+          <t>2026.01.21</t>
         </is>
       </c>
       <c r="C50" s="117" t="inlineStr">
@@ -15884,43 +15782,43 @@
         </is>
       </c>
       <c r="D50" s="118" t="n">
-        <v>9060</v>
+        <v>2710</v>
       </c>
       <c r="E50" s="118" t="n">
-        <v>13860</v>
+        <v>3700</v>
       </c>
       <c r="F50" s="122" t="n">
-        <v>0.65368</v>
+        <v>0.732432</v>
       </c>
       <c r="G50" s="118" t="n">
-        <v>1439.1</v>
+        <v>1475.7</v>
       </c>
       <c r="H50" s="120" t="n">
-        <v>13038246</v>
+        <v>3999147</v>
       </c>
       <c r="I50" s="120" t="n">
-        <v>18814</v>
+        <v>21617</v>
       </c>
       <c r="J50" s="120" t="n">
-        <v>6537</v>
+        <v>5493</v>
       </c>
       <c r="K50" s="120" t="n">
-        <v>5229</v>
+        <v>5859</v>
       </c>
       <c r="L50" s="121" t="n">
-        <v>13068826</v>
+        <v>4032116</v>
       </c>
       <c r="M50" s="115" t="n"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="116" t="inlineStr">
         <is>
-          <t>GPO458</t>
+          <t>GPO461</t>
         </is>
       </c>
       <c r="B51" s="116" t="inlineStr">
         <is>
-          <t>2025.12.29</t>
+          <t>2026.01.21</t>
         </is>
       </c>
       <c r="C51" s="117" t="inlineStr">
@@ -15929,308 +15827,308 @@
         </is>
       </c>
       <c r="D51" s="118" t="n">
-        <v>350</v>
+        <v>540</v>
       </c>
       <c r="E51" s="118" t="n">
-        <v>13860</v>
+        <v>3700</v>
       </c>
       <c r="F51" s="122" t="n">
-        <v>0.025253</v>
+        <v>0.145946</v>
       </c>
       <c r="G51" s="118" t="n">
-        <v>1439.1</v>
+        <v>1475.7</v>
       </c>
       <c r="H51" s="120" t="n">
-        <v>503685</v>
+        <v>796878</v>
       </c>
       <c r="I51" s="120" t="n">
-        <v>727</v>
+        <v>4307</v>
       </c>
       <c r="J51" s="120" t="n">
-        <v>253</v>
+        <v>1095</v>
       </c>
       <c r="K51" s="120" t="n">
-        <v>202</v>
+        <v>1168</v>
       </c>
       <c r="L51" s="121" t="n">
-        <v>504867</v>
+        <v>803448</v>
       </c>
       <c r="M51" s="115" t="n"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="116" t="inlineStr">
         <is>
-          <t>CPO680</t>
+          <t>MPO66</t>
         </is>
       </c>
       <c r="B52" s="116" t="inlineStr">
         <is>
-          <t>2026.01.13</t>
+          <t>2026.01.21</t>
         </is>
       </c>
       <c r="C52" s="117" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D52" s="118" t="n">
-        <v>252</v>
+        <v>9626.35</v>
       </c>
       <c r="E52" s="118" t="n">
-        <v>252</v>
+        <v>9626.35</v>
       </c>
       <c r="F52" s="122" t="n">
         <v>1</v>
       </c>
       <c r="G52" s="118" t="n">
-        <v>1479</v>
+        <v>1476</v>
       </c>
       <c r="H52" s="120" t="n">
-        <v>372708</v>
+        <v>14208493</v>
       </c>
       <c r="I52" s="120" t="n">
-        <v>29580</v>
+        <v>29520</v>
       </c>
       <c r="J52" s="120" t="n">
-        <v>2500</v>
+        <v>10000</v>
       </c>
       <c r="K52" s="120" t="n">
         <v>8000</v>
       </c>
       <c r="L52" s="121" t="n">
-        <v>412788</v>
+        <v>14256013</v>
       </c>
       <c r="M52" s="115" t="n"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="116" t="inlineStr">
         <is>
-          <t>GPO459</t>
+          <t>LPO001</t>
         </is>
       </c>
       <c r="B53" s="116" t="inlineStr">
         <is>
-          <t>2026.01.21</t>
+          <t>2026.01.30</t>
         </is>
       </c>
       <c r="C53" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Lemon</t>
         </is>
       </c>
       <c r="D53" s="118" t="n">
-        <v>450</v>
+        <v>5056.8</v>
       </c>
       <c r="E53" s="118" t="n">
-        <v>3700</v>
+        <v>5056.8</v>
       </c>
       <c r="F53" s="122" t="n">
-        <v>0.121622</v>
+        <v>1</v>
       </c>
       <c r="G53" s="118" t="n">
-        <v>1475.7</v>
+        <v>1445.5</v>
       </c>
       <c r="H53" s="120" t="n">
-        <v>664065</v>
+        <v>7309604</v>
       </c>
       <c r="I53" s="120" t="n">
-        <v>3590</v>
+        <v>28910</v>
       </c>
       <c r="J53" s="120" t="n">
-        <v>912</v>
+        <v>10000</v>
       </c>
       <c r="K53" s="120" t="n">
-        <v>973</v>
+        <v>8000</v>
       </c>
       <c r="L53" s="121" t="n">
-        <v>669540</v>
+        <v>7356514</v>
       </c>
       <c r="M53" s="115" t="n"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="116" t="inlineStr">
         <is>
-          <t>GPO460</t>
+          <t>CPO682</t>
         </is>
       </c>
       <c r="B54" s="116" t="inlineStr">
         <is>
-          <t>2026.01.21</t>
+          <t>2026.02.04</t>
         </is>
       </c>
       <c r="C54" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D54" s="118" t="n">
-        <v>2710</v>
+        <v>20174</v>
       </c>
       <c r="E54" s="118" t="n">
-        <v>3700</v>
+        <v>24794</v>
       </c>
       <c r="F54" s="122" t="n">
-        <v>0.732432</v>
+        <v>0.813665</v>
       </c>
       <c r="G54" s="118" t="n">
-        <v>1475.7</v>
+        <v>1454.7</v>
       </c>
       <c r="H54" s="120" t="n">
-        <v>3999147</v>
+        <v>29347118</v>
       </c>
       <c r="I54" s="120" t="n">
-        <v>21617</v>
+        <v>23673</v>
       </c>
       <c r="J54" s="120" t="n">
-        <v>5493</v>
+        <v>10171</v>
       </c>
       <c r="K54" s="120" t="n">
-        <v>5859</v>
+        <v>6509</v>
       </c>
       <c r="L54" s="121" t="n">
-        <v>4032116</v>
+        <v>29387471</v>
       </c>
       <c r="M54" s="115" t="n"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="116" t="inlineStr">
         <is>
-          <t>GPO461</t>
+          <t>CPO683</t>
         </is>
       </c>
       <c r="B55" s="116" t="inlineStr">
         <is>
-          <t>2026.01.21</t>
+          <t>2026.02.04</t>
         </is>
       </c>
       <c r="C55" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D55" s="118" t="n">
-        <v>540</v>
+        <v>4620</v>
       </c>
       <c r="E55" s="118" t="n">
-        <v>3700</v>
+        <v>24794</v>
       </c>
       <c r="F55" s="122" t="n">
-        <v>0.145946</v>
+        <v>0.186335</v>
       </c>
       <c r="G55" s="118" t="n">
-        <v>1475.7</v>
+        <v>1454.7</v>
       </c>
       <c r="H55" s="120" t="n">
-        <v>796878</v>
+        <v>6720714</v>
       </c>
       <c r="I55" s="120" t="n">
-        <v>4307</v>
+        <v>5421</v>
       </c>
       <c r="J55" s="120" t="n">
-        <v>1095</v>
+        <v>2329</v>
       </c>
       <c r="K55" s="120" t="n">
-        <v>1168</v>
+        <v>1491</v>
       </c>
       <c r="L55" s="121" t="n">
-        <v>803448</v>
+        <v>6729955</v>
       </c>
       <c r="M55" s="115" t="n"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="116" t="inlineStr">
         <is>
-          <t>MPO66</t>
+          <t>GPO462</t>
         </is>
       </c>
       <c r="B56" s="116" t="inlineStr">
         <is>
-          <t>2026.01.21</t>
+          <t>2026.02.04</t>
         </is>
       </c>
       <c r="C56" s="117" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D56" s="118" t="n">
-        <v>9626.35</v>
+        <v>1440</v>
       </c>
       <c r="E56" s="118" t="n">
-        <v>9626.35</v>
+        <v>11599.57</v>
       </c>
       <c r="F56" s="122" t="n">
-        <v>1</v>
+        <v>0.124143</v>
       </c>
       <c r="G56" s="118" t="n">
-        <v>1476</v>
+        <v>1453.6</v>
       </c>
       <c r="H56" s="120" t="n">
-        <v>14208493</v>
+        <v>2093184</v>
       </c>
       <c r="I56" s="120" t="n">
-        <v>29520</v>
+        <v>3609</v>
       </c>
       <c r="J56" s="120" t="n">
-        <v>10000</v>
+        <v>1241</v>
       </c>
       <c r="K56" s="120" t="n">
-        <v>8000</v>
+        <v>993</v>
       </c>
       <c r="L56" s="121" t="n">
-        <v>14256013</v>
+        <v>2099027</v>
       </c>
       <c r="M56" s="115" t="n"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="116" t="inlineStr">
         <is>
-          <t>LPO001</t>
+          <t>GPO463</t>
         </is>
       </c>
       <c r="B57" s="116" t="inlineStr">
         <is>
-          <t>2026.01.30</t>
+          <t>2026.02.04</t>
         </is>
       </c>
       <c r="C57" s="117" t="inlineStr">
         <is>
-          <t>Lemon</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D57" s="118" t="n">
-        <v>5056.8</v>
+        <v>4489</v>
       </c>
       <c r="E57" s="118" t="n">
-        <v>5056.8</v>
+        <v>11599.57</v>
       </c>
       <c r="F57" s="122" t="n">
-        <v>1</v>
+        <v>0.386997</v>
       </c>
       <c r="G57" s="118" t="n">
-        <v>1445.5</v>
+        <v>1453.6</v>
       </c>
       <c r="H57" s="120" t="n">
-        <v>7309604</v>
+        <v>6525210</v>
       </c>
       <c r="I57" s="120" t="n">
-        <v>28910</v>
+        <v>11251</v>
       </c>
       <c r="J57" s="120" t="n">
-        <v>10000</v>
+        <v>3870</v>
       </c>
       <c r="K57" s="120" t="n">
-        <v>8000</v>
+        <v>3096</v>
       </c>
       <c r="L57" s="121" t="n">
-        <v>7356514</v>
+        <v>6543427</v>
       </c>
       <c r="M57" s="115" t="n"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="116" t="inlineStr">
         <is>
-          <t>CPO682</t>
+          <t>GPO464</t>
         </is>
       </c>
       <c r="B58" s="116" t="inlineStr">
@@ -16240,47 +16138,47 @@
       </c>
       <c r="C58" s="117" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D58" s="118" t="n">
-        <v>20174</v>
+        <v>5670.57</v>
       </c>
       <c r="E58" s="118" t="n">
-        <v>24794</v>
+        <v>11599.57</v>
       </c>
       <c r="F58" s="122" t="n">
-        <v>0.813665</v>
+        <v>0.48886</v>
       </c>
       <c r="G58" s="118" t="n">
-        <v>1454.7</v>
+        <v>1453.6</v>
       </c>
       <c r="H58" s="120" t="n">
-        <v>29347118</v>
+        <v>8242741</v>
       </c>
       <c r="I58" s="120" t="n">
-        <v>23673</v>
+        <v>14212</v>
       </c>
       <c r="J58" s="120" t="n">
-        <v>10171</v>
+        <v>4889</v>
       </c>
       <c r="K58" s="120" t="n">
-        <v>6509</v>
+        <v>3911</v>
       </c>
       <c r="L58" s="121" t="n">
-        <v>29387471</v>
+        <v>8265753</v>
       </c>
       <c r="M58" s="115" t="n"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="116" t="inlineStr">
         <is>
-          <t>CPO683</t>
+          <t>CPO681</t>
         </is>
       </c>
       <c r="B59" s="116" t="inlineStr">
         <is>
-          <t>2026.02.04</t>
+          <t>2026.02.11</t>
         </is>
       </c>
       <c r="C59" s="117" t="inlineStr">
@@ -16289,178 +16187,178 @@
         </is>
       </c>
       <c r="D59" s="118" t="n">
-        <v>4620</v>
+        <v>26358</v>
       </c>
       <c r="E59" s="118" t="n">
-        <v>24794</v>
+        <v>26358</v>
       </c>
       <c r="F59" s="122" t="n">
-        <v>0.186335</v>
+        <v>1</v>
       </c>
       <c r="G59" s="118" t="n">
-        <v>1454.7</v>
+        <v>1460.7</v>
       </c>
       <c r="H59" s="120" t="n">
-        <v>6720714</v>
+        <v>38501131</v>
       </c>
       <c r="I59" s="120" t="n">
-        <v>5421</v>
+        <v>29214</v>
       </c>
       <c r="J59" s="120" t="n">
-        <v>2329</v>
+        <v>12500</v>
       </c>
       <c r="K59" s="120" t="n">
-        <v>1491</v>
+        <v>8000</v>
       </c>
       <c r="L59" s="121" t="n">
-        <v>6729955</v>
+        <v>38550845</v>
       </c>
       <c r="M59" s="115" t="n"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="116" t="inlineStr">
         <is>
-          <t>GPO462</t>
+          <t>CPO686</t>
         </is>
       </c>
       <c r="B60" s="116" t="inlineStr">
         <is>
-          <t>2026.02.04</t>
+          <t>2026.02.19</t>
         </is>
       </c>
       <c r="C60" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D60" s="118" t="n">
-        <v>1440</v>
+        <v>14793</v>
       </c>
       <c r="E60" s="118" t="n">
-        <v>11599.57</v>
+        <v>17538</v>
       </c>
       <c r="F60" s="122" t="n">
-        <v>0.124143</v>
+        <v>0.843483</v>
       </c>
       <c r="G60" s="118" t="n">
-        <v>1453.6</v>
+        <v>1451.7</v>
       </c>
       <c r="H60" s="120" t="n">
-        <v>2093184</v>
+        <v>21474998</v>
       </c>
       <c r="I60" s="120" t="n">
-        <v>3609</v>
+        <v>24490</v>
       </c>
       <c r="J60" s="120" t="n">
-        <v>1241</v>
+        <v>8435</v>
       </c>
       <c r="K60" s="120" t="n">
-        <v>993</v>
+        <v>6748</v>
       </c>
       <c r="L60" s="121" t="n">
-        <v>2099027</v>
+        <v>21514671</v>
       </c>
       <c r="M60" s="115" t="n"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="116" t="inlineStr">
         <is>
-          <t>GPO463</t>
+          <t>CPO689</t>
         </is>
       </c>
       <c r="B61" s="116" t="inlineStr">
         <is>
-          <t>2026.02.04</t>
+          <t>2026.02.19</t>
         </is>
       </c>
       <c r="C61" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D61" s="118" t="n">
-        <v>4489</v>
+        <v>2745</v>
       </c>
       <c r="E61" s="118" t="n">
-        <v>11599.57</v>
+        <v>17538</v>
       </c>
       <c r="F61" s="122" t="n">
-        <v>0.386997</v>
+        <v>0.156517</v>
       </c>
       <c r="G61" s="118" t="n">
-        <v>1453.6</v>
+        <v>1451.7</v>
       </c>
       <c r="H61" s="120" t="n">
-        <v>6525210</v>
+        <v>3984917</v>
       </c>
       <c r="I61" s="120" t="n">
-        <v>11251</v>
+        <v>4544</v>
       </c>
       <c r="J61" s="120" t="n">
-        <v>3870</v>
+        <v>1565</v>
       </c>
       <c r="K61" s="120" t="n">
-        <v>3096</v>
+        <v>1252</v>
       </c>
       <c r="L61" s="121" t="n">
-        <v>6543427</v>
+        <v>3992278</v>
       </c>
       <c r="M61" s="115" t="n"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="116" t="inlineStr">
         <is>
-          <t>GPO464</t>
+          <t>CPO667</t>
         </is>
       </c>
       <c r="B62" s="116" t="inlineStr">
         <is>
-          <t>2026.02.04</t>
+          <t>2026.02.27</t>
         </is>
       </c>
       <c r="C62" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D62" s="118" t="n">
-        <v>5670.57</v>
+        <v>5673</v>
       </c>
       <c r="E62" s="118" t="n">
-        <v>11599.57</v>
+        <v>142189</v>
       </c>
       <c r="F62" s="122" t="n">
-        <v>0.48886</v>
+        <v>0.039898</v>
       </c>
       <c r="G62" s="118" t="n">
-        <v>1453.6</v>
+        <v>1441.6</v>
       </c>
       <c r="H62" s="120" t="n">
-        <v>8242741</v>
+        <v>8178197</v>
       </c>
       <c r="I62" s="120" t="n">
-        <v>14212</v>
+        <v>1150</v>
       </c>
       <c r="J62" s="120" t="n">
-        <v>4889</v>
+        <v>499</v>
       </c>
       <c r="K62" s="120" t="n">
-        <v>3911</v>
+        <v>319</v>
       </c>
       <c r="L62" s="121" t="n">
-        <v>8265753</v>
+        <v>8180165</v>
       </c>
       <c r="M62" s="115" t="n"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="116" t="inlineStr">
         <is>
-          <t>CPO681</t>
+          <t>CPO685</t>
         </is>
       </c>
       <c r="B63" s="116" t="inlineStr">
         <is>
-          <t>2026.02.11</t>
+          <t>2026.02.27</t>
         </is>
       </c>
       <c r="C63" s="117" t="inlineStr">
@@ -16469,43 +16367,43 @@
         </is>
       </c>
       <c r="D63" s="118" t="n">
-        <v>26358</v>
+        <v>136516</v>
       </c>
       <c r="E63" s="118" t="n">
-        <v>26358</v>
+        <v>142189</v>
       </c>
       <c r="F63" s="122" t="n">
-        <v>1</v>
+        <v>0.960102</v>
       </c>
       <c r="G63" s="118" t="n">
-        <v>1460.7</v>
+        <v>1441.6</v>
       </c>
       <c r="H63" s="120" t="n">
-        <v>38501131</v>
+        <v>196801466</v>
       </c>
       <c r="I63" s="120" t="n">
-        <v>29214</v>
+        <v>27682</v>
       </c>
       <c r="J63" s="120" t="n">
-        <v>12500</v>
+        <v>12001</v>
       </c>
       <c r="K63" s="120" t="n">
-        <v>8000</v>
+        <v>7681</v>
       </c>
       <c r="L63" s="121" t="n">
-        <v>38550845</v>
+        <v>196848830</v>
       </c>
       <c r="M63" s="115" t="n"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="116" t="inlineStr">
         <is>
-          <t>CPO686</t>
+          <t>CPO678-2</t>
         </is>
       </c>
       <c r="B64" s="116" t="inlineStr">
         <is>
-          <t>2026.02.19</t>
+          <t>2026.03.06</t>
         </is>
       </c>
       <c r="C64" s="117" t="inlineStr">
@@ -16514,43 +16412,43 @@
         </is>
       </c>
       <c r="D64" s="118" t="n">
-        <v>14793</v>
+        <v>137850</v>
       </c>
       <c r="E64" s="118" t="n">
-        <v>17538</v>
+        <v>137850</v>
       </c>
       <c r="F64" s="122" t="n">
-        <v>0.843483</v>
+        <v>1</v>
       </c>
       <c r="G64" s="118" t="n">
-        <v>1451.7</v>
+        <v>1477.6</v>
       </c>
       <c r="H64" s="120" t="n">
-        <v>21474998</v>
+        <v>203687160</v>
       </c>
       <c r="I64" s="120" t="n">
-        <v>24490</v>
+        <v>29552</v>
       </c>
       <c r="J64" s="120" t="n">
-        <v>8435</v>
+        <v>12500</v>
       </c>
       <c r="K64" s="120" t="n">
-        <v>6748</v>
+        <v>8000</v>
       </c>
       <c r="L64" s="121" t="n">
-        <v>21514671</v>
+        <v>203737212</v>
       </c>
       <c r="M64" s="115" t="n"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="116" t="inlineStr">
         <is>
-          <t>CPO689</t>
+          <t>CPO690</t>
         </is>
       </c>
       <c r="B65" s="116" t="inlineStr">
         <is>
-          <t>2026.02.19</t>
+          <t>2026.04.01</t>
         </is>
       </c>
       <c r="C65" s="117" t="inlineStr">
@@ -16559,43 +16457,43 @@
         </is>
       </c>
       <c r="D65" s="118" t="n">
-        <v>2745</v>
+        <v>9740</v>
       </c>
       <c r="E65" s="118" t="n">
-        <v>17538</v>
+        <v>34354</v>
       </c>
       <c r="F65" s="122" t="n">
-        <v>0.156517</v>
+        <v>0.283519</v>
       </c>
       <c r="G65" s="118" t="n">
-        <v>1451.7</v>
+        <v>1505.7</v>
       </c>
       <c r="H65" s="120" t="n">
-        <v>3984917</v>
+        <v>14665518</v>
       </c>
       <c r="I65" s="120" t="n">
-        <v>4544</v>
+        <v>8538</v>
       </c>
       <c r="J65" s="120" t="n">
-        <v>1565</v>
+        <v>3544</v>
       </c>
       <c r="K65" s="120" t="n">
-        <v>1252</v>
+        <v>2268</v>
       </c>
       <c r="L65" s="121" t="n">
-        <v>3992278</v>
+        <v>14679868</v>
       </c>
       <c r="M65" s="115" t="n"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="116" t="inlineStr">
         <is>
-          <t>CPO667</t>
+          <t>CPO691</t>
         </is>
       </c>
       <c r="B66" s="116" t="inlineStr">
         <is>
-          <t>2026.02.27</t>
+          <t>2026.04.01</t>
         </is>
       </c>
       <c r="C66" s="117" t="inlineStr">
@@ -16604,128 +16502,128 @@
         </is>
       </c>
       <c r="D66" s="118" t="n">
-        <v>5673</v>
+        <v>24614</v>
       </c>
       <c r="E66" s="118" t="n">
-        <v>142189</v>
+        <v>34354</v>
       </c>
       <c r="F66" s="122" t="n">
-        <v>0.039898</v>
+        <v>0.716481</v>
       </c>
       <c r="G66" s="118" t="n">
-        <v>1441.6</v>
+        <v>1505.7</v>
       </c>
       <c r="H66" s="120" t="n">
-        <v>8178197</v>
+        <v>37061300</v>
       </c>
       <c r="I66" s="120" t="n">
-        <v>1150</v>
+        <v>21576</v>
       </c>
       <c r="J66" s="120" t="n">
-        <v>499</v>
+        <v>8956</v>
       </c>
       <c r="K66" s="120" t="n">
-        <v>319</v>
+        <v>5732</v>
       </c>
       <c r="L66" s="121" t="n">
-        <v>8180165</v>
+        <v>37097564</v>
       </c>
       <c r="M66" s="115" t="n"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="116" t="inlineStr">
         <is>
-          <t>CPO685</t>
+          <t>GPO467</t>
         </is>
       </c>
       <c r="B67" s="116" t="inlineStr">
         <is>
-          <t>2026.02.27</t>
+          <t>2026.04.01</t>
         </is>
       </c>
       <c r="C67" s="117" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D67" s="118" t="n">
-        <v>136516</v>
+        <v>1700</v>
       </c>
       <c r="E67" s="118" t="n">
-        <v>142189</v>
+        <v>6553.05</v>
       </c>
       <c r="F67" s="122" t="n">
-        <v>0.960102</v>
+        <v>0.259421</v>
       </c>
       <c r="G67" s="118" t="n">
-        <v>1441.6</v>
+        <v>1506.4</v>
       </c>
       <c r="H67" s="120" t="n">
-        <v>196801466</v>
+        <v>2560880</v>
       </c>
       <c r="I67" s="120" t="n">
-        <v>27682</v>
+        <v>7816</v>
       </c>
       <c r="J67" s="120" t="n">
-        <v>12001</v>
+        <v>2594</v>
       </c>
       <c r="K67" s="120" t="n">
-        <v>7681</v>
+        <v>2075</v>
       </c>
       <c r="L67" s="121" t="n">
-        <v>196848830</v>
+        <v>2573365</v>
       </c>
       <c r="M67" s="115" t="n"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="116" t="inlineStr">
         <is>
-          <t>CPO678-2</t>
+          <t>GPO469</t>
         </is>
       </c>
       <c r="B68" s="116" t="inlineStr">
         <is>
-          <t>2026.03.06</t>
+          <t>2026.04.01</t>
         </is>
       </c>
       <c r="C68" s="117" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D68" s="118" t="n">
-        <v>137850</v>
+        <v>3993.05</v>
       </c>
       <c r="E68" s="118" t="n">
-        <v>137850</v>
+        <v>6553.05</v>
       </c>
       <c r="F68" s="122" t="n">
-        <v>1</v>
+        <v>0.6093420000000001</v>
       </c>
       <c r="G68" s="118" t="n">
-        <v>1477.6</v>
+        <v>1506.4</v>
       </c>
       <c r="H68" s="120" t="n">
-        <v>203687160</v>
+        <v>6015131</v>
       </c>
       <c r="I68" s="120" t="n">
-        <v>29552</v>
+        <v>18358</v>
       </c>
       <c r="J68" s="120" t="n">
-        <v>12500</v>
+        <v>6093</v>
       </c>
       <c r="K68" s="120" t="n">
-        <v>8000</v>
+        <v>4875</v>
       </c>
       <c r="L68" s="121" t="n">
-        <v>203737212</v>
+        <v>6044457</v>
       </c>
       <c r="M68" s="115" t="n"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="116" t="inlineStr">
         <is>
-          <t>CPO690</t>
+          <t>GPO470</t>
         </is>
       </c>
       <c r="B69" s="116" t="inlineStr">
@@ -16735,42 +16633,42 @@
       </c>
       <c r="C69" s="117" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D69" s="118" t="n">
-        <v>9740</v>
+        <v>360</v>
       </c>
       <c r="E69" s="118" t="n">
-        <v>34354</v>
+        <v>6553.05</v>
       </c>
       <c r="F69" s="122" t="n">
-        <v>0.283519</v>
+        <v>0.054936</v>
       </c>
       <c r="G69" s="118" t="n">
-        <v>1505.7</v>
+        <v>1506.4</v>
       </c>
       <c r="H69" s="120" t="n">
-        <v>14665518</v>
+        <v>542304</v>
       </c>
       <c r="I69" s="120" t="n">
-        <v>8538</v>
+        <v>1655</v>
       </c>
       <c r="J69" s="120" t="n">
-        <v>3544</v>
+        <v>549</v>
       </c>
       <c r="K69" s="120" t="n">
-        <v>2268</v>
+        <v>439</v>
       </c>
       <c r="L69" s="121" t="n">
-        <v>14679868</v>
+        <v>544947</v>
       </c>
       <c r="M69" s="115" t="n"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="116" t="inlineStr">
         <is>
-          <t>CPO691</t>
+          <t>GPO471</t>
         </is>
       </c>
       <c r="B70" s="116" t="inlineStr">
@@ -16780,47 +16678,47 @@
       </c>
       <c r="C70" s="117" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D70" s="118" t="n">
-        <v>24614</v>
+        <v>500</v>
       </c>
       <c r="E70" s="118" t="n">
-        <v>34354</v>
+        <v>6553.05</v>
       </c>
       <c r="F70" s="122" t="n">
-        <v>0.716481</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="G70" s="118" t="n">
-        <v>1505.7</v>
+        <v>1506.4</v>
       </c>
       <c r="H70" s="120" t="n">
-        <v>37061300</v>
+        <v>753200</v>
       </c>
       <c r="I70" s="120" t="n">
-        <v>21576</v>
+        <v>2299</v>
       </c>
       <c r="J70" s="120" t="n">
-        <v>8956</v>
+        <v>763</v>
       </c>
       <c r="K70" s="120" t="n">
-        <v>5732</v>
+        <v>610</v>
       </c>
       <c r="L70" s="121" t="n">
-        <v>37097564</v>
+        <v>756872</v>
       </c>
       <c r="M70" s="115" t="n"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="116" t="inlineStr">
         <is>
-          <t>GPO467</t>
+          <t>GPO468-1</t>
         </is>
       </c>
       <c r="B71" s="116" t="inlineStr">
         <is>
-          <t>2026.04.01</t>
+          <t>2026.04.14</t>
         </is>
       </c>
       <c r="C71" s="117" t="inlineStr">
@@ -16829,43 +16727,43 @@
         </is>
       </c>
       <c r="D71" s="118" t="n">
-        <v>1700</v>
+        <v>36190</v>
       </c>
       <c r="E71" s="118" t="n">
-        <v>6553.05</v>
+        <v>57650</v>
       </c>
       <c r="F71" s="122" t="n">
-        <v>0.259421</v>
+        <v>0.627754</v>
       </c>
       <c r="G71" s="118" t="n">
-        <v>1506.4</v>
+        <v>1481.9</v>
       </c>
       <c r="H71" s="120" t="n">
-        <v>2560880</v>
+        <v>53629961</v>
       </c>
       <c r="I71" s="120" t="n">
-        <v>7816</v>
+        <v>18605</v>
       </c>
       <c r="J71" s="120" t="n">
-        <v>2594</v>
+        <v>7847</v>
       </c>
       <c r="K71" s="120" t="n">
-        <v>2075</v>
+        <v>5022</v>
       </c>
       <c r="L71" s="121" t="n">
-        <v>2573365</v>
+        <v>53661435</v>
       </c>
       <c r="M71" s="115" t="n"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="116" t="inlineStr">
         <is>
-          <t>GPO469</t>
+          <t>GPO472</t>
         </is>
       </c>
       <c r="B72" s="116" t="inlineStr">
         <is>
-          <t>2026.04.01</t>
+          <t>2026.04.14</t>
         </is>
       </c>
       <c r="C72" s="117" t="inlineStr">
@@ -16874,43 +16772,43 @@
         </is>
       </c>
       <c r="D72" s="118" t="n">
-        <v>3993.05</v>
+        <v>180</v>
       </c>
       <c r="E72" s="118" t="n">
-        <v>6553.05</v>
+        <v>57650</v>
       </c>
       <c r="F72" s="122" t="n">
-        <v>0.6093420000000001</v>
+        <v>0.003122</v>
       </c>
       <c r="G72" s="118" t="n">
-        <v>1506.4</v>
+        <v>1481.9</v>
       </c>
       <c r="H72" s="120" t="n">
-        <v>6015131</v>
+        <v>266742</v>
       </c>
       <c r="I72" s="120" t="n">
-        <v>18358</v>
+        <v>93</v>
       </c>
       <c r="J72" s="120" t="n">
-        <v>6093</v>
+        <v>39</v>
       </c>
       <c r="K72" s="120" t="n">
-        <v>4875</v>
+        <v>25</v>
       </c>
       <c r="L72" s="121" t="n">
-        <v>6044457</v>
+        <v>266899</v>
       </c>
       <c r="M72" s="115" t="n"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="116" t="inlineStr">
         <is>
-          <t>GPO470</t>
+          <t>GPO468-2</t>
         </is>
       </c>
       <c r="B73" s="116" t="inlineStr">
         <is>
-          <t>2026.04.01</t>
+          <t>2026.04.14</t>
         </is>
       </c>
       <c r="C73" s="117" t="inlineStr">
@@ -16919,223 +16817,221 @@
         </is>
       </c>
       <c r="D73" s="118" t="n">
-        <v>360</v>
+        <v>21280</v>
       </c>
       <c r="E73" s="118" t="n">
-        <v>6553.05</v>
+        <v>57650</v>
       </c>
       <c r="F73" s="122" t="n">
-        <v>0.054936</v>
+        <v>0.369124</v>
       </c>
       <c r="G73" s="118" t="n">
-        <v>1506.4</v>
+        <v>1481.9</v>
       </c>
       <c r="H73" s="120" t="n">
-        <v>542304</v>
+        <v>31534832</v>
       </c>
       <c r="I73" s="120" t="n">
-        <v>1655</v>
+        <v>10940</v>
       </c>
       <c r="J73" s="120" t="n">
-        <v>549</v>
+        <v>4614</v>
       </c>
       <c r="K73" s="120" t="n">
-        <v>439</v>
+        <v>2953</v>
       </c>
       <c r="L73" s="121" t="n">
-        <v>544947</v>
+        <v>31553339</v>
       </c>
       <c r="M73" s="115" t="n"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="116" t="inlineStr">
         <is>
-          <t>GPO471</t>
+          <t>CPO692-1</t>
         </is>
       </c>
       <c r="B74" s="116" t="inlineStr">
         <is>
-          <t>2026.04.01</t>
+          <t>2026.04.22</t>
         </is>
       </c>
       <c r="C74" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D74" s="118" t="n">
-        <v>500</v>
+        <v>11000</v>
       </c>
       <c r="E74" s="118" t="n">
-        <v>6553.05</v>
+        <v>297580</v>
       </c>
       <c r="F74" s="122" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.036965</v>
       </c>
       <c r="G74" s="118" t="n">
-        <v>1506.4</v>
+        <v>1482.8</v>
       </c>
       <c r="H74" s="120" t="n">
-        <v>753200</v>
+        <v>16310800</v>
       </c>
       <c r="I74" s="120" t="n">
-        <v>2299</v>
+        <v>1096</v>
       </c>
       <c r="J74" s="120" t="n">
-        <v>763</v>
+        <v>462</v>
       </c>
       <c r="K74" s="120" t="n">
-        <v>610</v>
+        <v>296</v>
       </c>
       <c r="L74" s="121" t="n">
-        <v>756872</v>
+        <v>16312654</v>
       </c>
       <c r="M74" s="115" t="n"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="116" t="inlineStr">
         <is>
-          <t>GPO468-1</t>
+          <t>CPO692-2</t>
         </is>
       </c>
       <c r="B75" s="116" t="inlineStr">
         <is>
-          <t>2026.04.14</t>
+          <t>2026.04.22</t>
         </is>
       </c>
       <c r="C75" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D75" s="118" t="n">
-        <v>36190</v>
+        <v>286580</v>
       </c>
       <c r="E75" s="118" t="n">
-        <v>57650</v>
+        <v>297580</v>
       </c>
       <c r="F75" s="122" t="n">
-        <v>0.627754</v>
+        <v>0.963035</v>
       </c>
       <c r="G75" s="118" t="n">
-        <v>1481.9</v>
+        <v>1482.8</v>
       </c>
       <c r="H75" s="120" t="n">
-        <v>53629961</v>
+        <v>424940824</v>
       </c>
       <c r="I75" s="120" t="n">
-        <v>18605</v>
+        <v>28560</v>
       </c>
       <c r="J75" s="120" t="n">
-        <v>7847</v>
+        <v>12038</v>
       </c>
       <c r="K75" s="120" t="n">
-        <v>5022</v>
+        <v>7704</v>
       </c>
       <c r="L75" s="121" t="n">
-        <v>53661435</v>
+        <v>424989126</v>
       </c>
       <c r="M75" s="115" t="n"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="116" t="inlineStr">
         <is>
-          <t>GPO472</t>
+          <t>EPO18</t>
         </is>
       </c>
       <c r="B76" s="116" t="inlineStr">
         <is>
-          <t>2026.04.14</t>
+          <t>2026.04.22</t>
         </is>
       </c>
       <c r="C76" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>MAICO Italia</t>
         </is>
       </c>
       <c r="D76" s="118" t="n">
-        <v>180</v>
+        <v>4388.4</v>
       </c>
       <c r="E76" s="118" t="n">
-        <v>57650</v>
+        <v>4388.4</v>
       </c>
       <c r="F76" s="122" t="n">
-        <v>0.003122</v>
+        <v>1</v>
       </c>
       <c r="G76" s="118" t="n">
-        <v>1481.9</v>
+        <v>1741.08</v>
       </c>
       <c r="H76" s="120" t="n">
-        <v>266742</v>
+        <v>7640555</v>
       </c>
       <c r="I76" s="120" t="n">
-        <v>93</v>
+        <v>43527</v>
       </c>
       <c r="J76" s="120" t="n">
-        <v>39</v>
+        <v>10000</v>
       </c>
       <c r="K76" s="120" t="n">
-        <v>25</v>
+        <v>8000</v>
       </c>
       <c r="L76" s="121" t="n">
-        <v>266899</v>
-      </c>
-      <c r="M76" s="115" t="n"/>
+        <v>7702082</v>
+      </c>
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="116" t="inlineStr">
         <is>
-          <t>GPO468-2</t>
+          <t>CPO694</t>
         </is>
       </c>
       <c r="B77" s="116" t="inlineStr">
         <is>
-          <t>2026.04.14</t>
+          <t>2026.05.04</t>
         </is>
       </c>
       <c r="C77" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D77" s="118" t="n">
-        <v>21280</v>
+        <v>17404</v>
       </c>
       <c r="E77" s="118" t="n">
-        <v>57650</v>
+        <v>21439</v>
       </c>
       <c r="F77" s="122" t="n">
-        <v>0.369124</v>
+        <v>0.811792</v>
       </c>
       <c r="G77" s="118" t="n">
-        <v>1481.9</v>
+        <v>1474.9</v>
       </c>
       <c r="H77" s="120" t="n">
-        <v>31534832</v>
+        <v>25669160</v>
       </c>
       <c r="I77" s="120" t="n">
-        <v>10940</v>
+        <v>23946</v>
       </c>
       <c r="J77" s="120" t="n">
-        <v>4614</v>
+        <v>10147</v>
       </c>
       <c r="K77" s="120" t="n">
-        <v>2953</v>
+        <v>6494</v>
       </c>
       <c r="L77" s="121" t="n">
-        <v>31553339</v>
-      </c>
-      <c r="M77" s="115" t="n"/>
+        <v>25709747</v>
+      </c>
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="116" t="inlineStr">
         <is>
-          <t>CPO692-1</t>
+          <t>CPO695-1</t>
         </is>
       </c>
       <c r="B78" s="116" t="inlineStr">
         <is>
-          <t>2026.04.22</t>
+          <t>2026.05.04</t>
         </is>
       </c>
       <c r="C78" s="117" t="inlineStr">
@@ -17144,43 +17040,42 @@
         </is>
       </c>
       <c r="D78" s="118" t="n">
-        <v>11000</v>
+        <v>2058</v>
       </c>
       <c r="E78" s="118" t="n">
-        <v>297580</v>
+        <v>21439</v>
       </c>
       <c r="F78" s="122" t="n">
-        <v>0.036965</v>
+        <v>0.09599299999999999</v>
       </c>
       <c r="G78" s="118" t="n">
-        <v>1482.8</v>
+        <v>1474.9</v>
       </c>
       <c r="H78" s="120" t="n">
-        <v>16310800</v>
+        <v>3035344</v>
       </c>
       <c r="I78" s="120" t="n">
-        <v>1096</v>
+        <v>2832</v>
       </c>
       <c r="J78" s="120" t="n">
-        <v>462</v>
+        <v>1200</v>
       </c>
       <c r="K78" s="120" t="n">
-        <v>296</v>
+        <v>768</v>
       </c>
       <c r="L78" s="121" t="n">
-        <v>16312654</v>
-      </c>
-      <c r="M78" s="115" t="n"/>
+        <v>3040144</v>
+      </c>
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="116" t="inlineStr">
         <is>
-          <t>CPO692-2</t>
+          <t>CPO695-2</t>
         </is>
       </c>
       <c r="B79" s="116" t="inlineStr">
         <is>
-          <t>2026.04.22</t>
+          <t>2026.05.04</t>
         </is>
       </c>
       <c r="C79" s="117" t="inlineStr">
@@ -17189,67 +17084,66 @@
         </is>
       </c>
       <c r="D79" s="118" t="n">
-        <v>286580</v>
+        <v>1977</v>
       </c>
       <c r="E79" s="118" t="n">
-        <v>297580</v>
+        <v>21439</v>
       </c>
       <c r="F79" s="122" t="n">
-        <v>0.963035</v>
+        <v>0.09221500000000001</v>
       </c>
       <c r="G79" s="118" t="n">
-        <v>1482.8</v>
+        <v>1474.9</v>
       </c>
       <c r="H79" s="120" t="n">
-        <v>424940824</v>
+        <v>2915877</v>
       </c>
       <c r="I79" s="120" t="n">
-        <v>28560</v>
+        <v>2720</v>
       </c>
       <c r="J79" s="120" t="n">
-        <v>12038</v>
+        <v>1153</v>
       </c>
       <c r="K79" s="120" t="n">
-        <v>7704</v>
+        <v>738</v>
       </c>
       <c r="L79" s="121" t="n">
-        <v>424989126</v>
-      </c>
-      <c r="M79" s="115" t="n"/>
+        <v>2920488</v>
+      </c>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="116" t="inlineStr">
         <is>
-          <t>EPO18</t>
+          <t>IPO016</t>
         </is>
       </c>
       <c r="B80" s="116" t="inlineStr">
         <is>
-          <t>2026.04.22</t>
+          <t>2026.05.04</t>
         </is>
       </c>
       <c r="C80" s="117" t="inlineStr">
         <is>
-          <t>MAICO Italia</t>
+          <t>Integ</t>
         </is>
       </c>
       <c r="D80" s="118" t="n">
-        <v>4388.4</v>
+        <v>6800</v>
       </c>
       <c r="E80" s="118" t="n">
-        <v>4388.4</v>
+        <v>6800</v>
       </c>
       <c r="F80" s="122" t="n">
         <v>1</v>
       </c>
       <c r="G80" s="118" t="n">
-        <v>1741.08</v>
+        <v>1475.2</v>
       </c>
       <c r="H80" s="120" t="n">
-        <v>7640555</v>
+        <v>10031360</v>
       </c>
       <c r="I80" s="120" t="n">
-        <v>43527</v>
+        <v>29504</v>
       </c>
       <c r="J80" s="120" t="n">
         <v>10000</v>
@@ -17258,62 +17152,62 @@
         <v>8000</v>
       </c>
       <c r="L80" s="121" t="n">
-        <v>7702082</v>
+        <v>10078864</v>
       </c>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="116" t="inlineStr">
         <is>
-          <t>CPO694</t>
+          <t>GPO478</t>
         </is>
       </c>
       <c r="B81" s="116" t="inlineStr">
         <is>
-          <t>2026.05.04</t>
+          <t>2026.05.19</t>
         </is>
       </c>
       <c r="C81" s="117" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D81" s="118" t="n">
-        <v>17404</v>
+        <v>180</v>
       </c>
       <c r="E81" s="118" t="n">
-        <v>21439</v>
+        <v>180</v>
       </c>
       <c r="F81" s="122" t="n">
-        <v>0.811792</v>
+        <v>1</v>
       </c>
       <c r="G81" s="118" t="n">
-        <v>1474.9</v>
+        <v>1518.9</v>
       </c>
       <c r="H81" s="120" t="n">
-        <v>25669160</v>
+        <v>273402</v>
       </c>
       <c r="I81" s="120" t="n">
-        <v>23946</v>
+        <v>30378</v>
       </c>
       <c r="J81" s="120" t="n">
-        <v>10147</v>
+        <v>2500</v>
       </c>
       <c r="K81" s="120" t="n">
-        <v>6494</v>
+        <v>8000</v>
       </c>
       <c r="L81" s="121" t="n">
-        <v>25709747</v>
+        <v>314280</v>
       </c>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="116" t="inlineStr">
         <is>
-          <t>CPO695-1</t>
+          <t>CPO698</t>
         </is>
       </c>
       <c r="B82" s="116" t="inlineStr">
         <is>
-          <t>2026.05.04</t>
+          <t>2026.05.20</t>
         </is>
       </c>
       <c r="C82" s="117" t="inlineStr">
@@ -17322,130 +17216,131 @@
         </is>
       </c>
       <c r="D82" s="118" t="n">
-        <v>2058</v>
+        <v>4290</v>
       </c>
       <c r="E82" s="118" t="n">
-        <v>21439</v>
+        <v>4290</v>
       </c>
       <c r="F82" s="122" t="n">
-        <v>0.09599299999999999</v>
+        <v>1</v>
       </c>
       <c r="G82" s="118" t="n">
-        <v>1474.9</v>
+        <v>1510.6</v>
       </c>
       <c r="H82" s="120" t="n">
-        <v>3035344</v>
+        <v>6480474</v>
       </c>
       <c r="I82" s="120" t="n">
-        <v>2832</v>
+        <v>30212</v>
       </c>
       <c r="J82" s="120" t="n">
-        <v>1200</v>
+        <v>7500</v>
       </c>
       <c r="K82" s="120" t="n">
-        <v>768</v>
+        <v>8000</v>
       </c>
       <c r="L82" s="121" t="n">
-        <v>3040144</v>
-      </c>
+        <v>6526186</v>
+      </c>
+      <c r="M82" s="40" t="n"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="116" t="inlineStr">
         <is>
-          <t>CPO695-2</t>
+          <t>GPO473-1</t>
         </is>
       </c>
       <c r="B83" s="116" t="inlineStr">
         <is>
-          <t>2026.05.04</t>
+          <t>2026.05.29</t>
         </is>
       </c>
       <c r="C83" s="117" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D83" s="118" t="n">
-        <v>1977</v>
+        <v>98800</v>
       </c>
       <c r="E83" s="118" t="n">
-        <v>21439</v>
+        <v>99140</v>
       </c>
       <c r="F83" s="122" t="n">
-        <v>0.09221500000000001</v>
+        <v>0.996571</v>
       </c>
       <c r="G83" s="118" t="n">
-        <v>1474.9</v>
+        <v>1502.8</v>
       </c>
       <c r="H83" s="120" t="n">
-        <v>2915877</v>
+        <v>148476640</v>
       </c>
       <c r="I83" s="120" t="n">
-        <v>2720</v>
+        <v>29953</v>
       </c>
       <c r="J83" s="120" t="n">
-        <v>1153</v>
+        <v>12457</v>
       </c>
       <c r="K83" s="120" t="n">
-        <v>738</v>
+        <v>7973</v>
       </c>
       <c r="L83" s="121" t="n">
-        <v>2920488</v>
+        <v>148527023</v>
       </c>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="116" t="inlineStr">
         <is>
-          <t>IPO016</t>
+          <t>GPO480</t>
         </is>
       </c>
       <c r="B84" s="116" t="inlineStr">
         <is>
-          <t>2026.05.04</t>
+          <t>2026.05.29</t>
         </is>
       </c>
       <c r="C84" s="117" t="inlineStr">
         <is>
-          <t>Integ</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D84" s="118" t="n">
-        <v>6800</v>
+        <v>250</v>
       </c>
       <c r="E84" s="118" t="n">
-        <v>6800</v>
+        <v>99140</v>
       </c>
       <c r="F84" s="122" t="n">
-        <v>1</v>
+        <v>0.002522</v>
       </c>
       <c r="G84" s="118" t="n">
-        <v>1475.2</v>
+        <v>1502.8</v>
       </c>
       <c r="H84" s="120" t="n">
-        <v>10031360</v>
+        <v>375700</v>
       </c>
       <c r="I84" s="120" t="n">
-        <v>29504</v>
+        <v>76</v>
       </c>
       <c r="J84" s="120" t="n">
-        <v>10000</v>
+        <v>32</v>
       </c>
       <c r="K84" s="120" t="n">
-        <v>8000</v>
+        <v>20</v>
       </c>
       <c r="L84" s="121" t="n">
-        <v>10078864</v>
+        <v>375828</v>
       </c>
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="116" t="inlineStr">
         <is>
-          <t>GPO478</t>
+          <t>GPO479</t>
         </is>
       </c>
       <c r="B85" s="116" t="inlineStr">
         <is>
-          <t>2026.05.19</t>
+          <t>2026.05.29</t>
         </is>
       </c>
       <c r="C85" s="117" t="inlineStr">
@@ -17454,42 +17349,42 @@
         </is>
       </c>
       <c r="D85" s="118" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="E85" s="118" t="n">
-        <v>180</v>
+        <v>99140</v>
       </c>
       <c r="F85" s="122" t="n">
-        <v>1</v>
+        <v>0.000908</v>
       </c>
       <c r="G85" s="118" t="n">
-        <v>1518.9</v>
+        <v>1502.8</v>
       </c>
       <c r="H85" s="120" t="n">
-        <v>273402</v>
+        <v>135252</v>
       </c>
       <c r="I85" s="120" t="n">
-        <v>30378</v>
+        <v>27</v>
       </c>
       <c r="J85" s="120" t="n">
-        <v>2500</v>
+        <v>11</v>
       </c>
       <c r="K85" s="120" t="n">
-        <v>8000</v>
+        <v>7</v>
       </c>
       <c r="L85" s="121" t="n">
-        <v>314280</v>
+        <v>135297</v>
       </c>
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="116" t="inlineStr">
         <is>
-          <t>CPO698</t>
+          <t>CPO697</t>
         </is>
       </c>
       <c r="B86" s="116" t="inlineStr">
         <is>
-          <t>2026.05.20</t>
+          <t>2026.05.29</t>
         </is>
       </c>
       <c r="C86" s="117" t="inlineStr">
@@ -17498,38 +17393,37 @@
         </is>
       </c>
       <c r="D86" s="118" t="n">
-        <v>4290</v>
+        <v>15289</v>
       </c>
       <c r="E86" s="118" t="n">
-        <v>4290</v>
+        <v>101638</v>
       </c>
       <c r="F86" s="122" t="n">
-        <v>1</v>
+        <v>0.150426</v>
       </c>
       <c r="G86" s="118" t="n">
-        <v>1510.6</v>
+        <v>1502.7</v>
       </c>
       <c r="H86" s="120" t="n">
-        <v>6480474</v>
+        <v>22974780</v>
       </c>
       <c r="I86" s="120" t="n">
-        <v>30212</v>
+        <v>4521</v>
       </c>
       <c r="J86" s="120" t="n">
-        <v>7500</v>
+        <v>1880</v>
       </c>
       <c r="K86" s="120" t="n">
-        <v>8000</v>
+        <v>1203</v>
       </c>
       <c r="L86" s="121" t="n">
-        <v>6526186</v>
-      </c>
-      <c r="M86" s="40" t="n"/>
+        <v>22982384</v>
+      </c>
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="116" t="inlineStr">
         <is>
-          <t>GPO473-1</t>
+          <t>CPO696-1</t>
         </is>
       </c>
       <c r="B87" s="116" t="inlineStr">
@@ -17539,41 +17433,41 @@
       </c>
       <c r="C87" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D87" s="118" t="n">
-        <v>98800</v>
+        <v>78209</v>
       </c>
       <c r="E87" s="118" t="n">
-        <v>99140</v>
+        <v>101638</v>
       </c>
       <c r="F87" s="122" t="n">
-        <v>0.996571</v>
+        <v>0.769486</v>
       </c>
       <c r="G87" s="118" t="n">
-        <v>1502.8</v>
+        <v>1502.7</v>
       </c>
       <c r="H87" s="120" t="n">
-        <v>148476640</v>
+        <v>117524664</v>
       </c>
       <c r="I87" s="120" t="n">
-        <v>29953</v>
+        <v>23126</v>
       </c>
       <c r="J87" s="120" t="n">
-        <v>12457</v>
+        <v>9619</v>
       </c>
       <c r="K87" s="120" t="n">
-        <v>7973</v>
+        <v>6156</v>
       </c>
       <c r="L87" s="121" t="n">
-        <v>148527023</v>
+        <v>117563565</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="116" t="inlineStr">
         <is>
-          <t>GPO480</t>
+          <t>CPO696-2</t>
         </is>
       </c>
       <c r="B88" s="116" t="inlineStr">
@@ -17583,349 +17477,357 @@
       </c>
       <c r="C88" s="117" t="inlineStr">
         <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D88" s="118" t="n">
+        <v>8140</v>
+      </c>
+      <c r="E88" s="118" t="n">
+        <v>101638</v>
+      </c>
+      <c r="F88" s="122" t="n">
+        <v>0.08008800000000001</v>
+      </c>
+      <c r="G88" s="118" t="n">
+        <v>1502.7</v>
+      </c>
+      <c r="H88" s="120" t="n">
+        <v>12231978</v>
+      </c>
+      <c r="I88" s="120" t="n">
+        <v>2407</v>
+      </c>
+      <c r="J88" s="120" t="n">
+        <v>1001</v>
+      </c>
+      <c r="K88" s="120" t="n">
+        <v>641</v>
+      </c>
+      <c r="L88" s="121" t="n">
+        <v>12236027</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="234" t="inlineStr">
+        <is>
+          <t>GPO481</t>
+        </is>
+      </c>
+      <c r="B89" s="234" t="inlineStr">
+        <is>
+          <t>2026.06.10</t>
+        </is>
+      </c>
+      <c r="C89" s="235" t="inlineStr">
+        <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D88" s="118" t="n">
-        <v>250</v>
-      </c>
-      <c r="E88" s="118" t="n">
-        <v>99140</v>
-      </c>
-      <c r="F88" s="122" t="n">
-        <v>0.002522</v>
-      </c>
-      <c r="G88" s="118" t="n">
-        <v>1502.8</v>
-      </c>
-      <c r="H88" s="120" t="n">
-        <v>375700</v>
-      </c>
-      <c r="I88" s="120" t="n">
-        <v>76</v>
-      </c>
-      <c r="J88" s="120" t="n">
-        <v>32</v>
-      </c>
-      <c r="K88" s="120" t="n">
-        <v>20</v>
-      </c>
-      <c r="L88" s="121" t="n">
-        <v>375828</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="116" t="inlineStr">
-        <is>
-          <t>GPO479</t>
-        </is>
-      </c>
-      <c r="B89" s="116" t="inlineStr">
-        <is>
-          <t>2026.05.29</t>
-        </is>
-      </c>
-      <c r="C89" s="117" t="inlineStr">
+      <c r="D89" s="236" t="n">
+        <v>500</v>
+      </c>
+      <c r="E89" s="236" t="n">
+        <v>119060</v>
+      </c>
+      <c r="F89" s="240" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="G89" s="236" t="n">
+        <v>1525.3</v>
+      </c>
+      <c r="H89" s="238" t="n">
+        <v>762650</v>
+      </c>
+      <c r="I89" s="238" t="n">
+        <v>128</v>
+      </c>
+      <c r="J89" s="238" t="n">
+        <v>52</v>
+      </c>
+      <c r="K89" s="238" t="n">
+        <v>34</v>
+      </c>
+      <c r="L89" s="239" t="n">
+        <v>762864</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="234" t="inlineStr">
+        <is>
+          <t>GPO473-2</t>
+        </is>
+      </c>
+      <c r="B90" s="234" t="inlineStr">
+        <is>
+          <t>2026.06.10</t>
+        </is>
+      </c>
+      <c r="C90" s="235" t="inlineStr">
         <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D89" s="118" t="n">
-        <v>90</v>
-      </c>
-      <c r="E89" s="118" t="n">
-        <v>99140</v>
-      </c>
-      <c r="F89" s="122" t="n">
-        <v>0.000908</v>
-      </c>
-      <c r="G89" s="118" t="n">
-        <v>1502.8</v>
-      </c>
-      <c r="H89" s="120" t="n">
-        <v>135252</v>
-      </c>
-      <c r="I89" s="120" t="n">
-        <v>27</v>
-      </c>
-      <c r="J89" s="120" t="n">
-        <v>11</v>
-      </c>
-      <c r="K89" s="120" t="n">
-        <v>7</v>
-      </c>
-      <c r="L89" s="121" t="n">
-        <v>135297</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="116" t="inlineStr">
-        <is>
-          <t>CPO697</t>
-        </is>
-      </c>
-      <c r="B90" s="116" t="inlineStr">
-        <is>
-          <t>2026.05.29</t>
-        </is>
-      </c>
-      <c r="C90" s="117" t="inlineStr">
+      <c r="D90" s="236" t="n">
+        <v>69160</v>
+      </c>
+      <c r="E90" s="236" t="n">
+        <v>119060</v>
+      </c>
+      <c r="F90" s="240" t="n">
+        <v>0.580884</v>
+      </c>
+      <c r="G90" s="236" t="n">
+        <v>1525.3</v>
+      </c>
+      <c r="H90" s="238" t="n">
+        <v>105489748</v>
+      </c>
+      <c r="I90" s="238" t="n">
+        <v>17720</v>
+      </c>
+      <c r="J90" s="238" t="n">
+        <v>7261</v>
+      </c>
+      <c r="K90" s="238" t="n">
+        <v>4647</v>
+      </c>
+      <c r="L90" s="239" t="n">
+        <v>105519376</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="234" t="inlineStr">
+        <is>
+          <t>GPO473-3</t>
+        </is>
+      </c>
+      <c r="B91" s="234" t="inlineStr">
+        <is>
+          <t>2026.06.10</t>
+        </is>
+      </c>
+      <c r="C91" s="235" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D91" s="236" t="n">
+        <v>49400</v>
+      </c>
+      <c r="E91" s="236" t="n">
+        <v>119060</v>
+      </c>
+      <c r="F91" s="240" t="n">
+        <v>0.414917</v>
+      </c>
+      <c r="G91" s="236" t="n">
+        <v>1525.3</v>
+      </c>
+      <c r="H91" s="238" t="n">
+        <v>75349820</v>
+      </c>
+      <c r="I91" s="238" t="n">
+        <v>12657</v>
+      </c>
+      <c r="J91" s="238" t="n">
+        <v>5186</v>
+      </c>
+      <c r="K91" s="238" t="n">
+        <v>3319</v>
+      </c>
+      <c r="L91" s="239" t="n">
+        <v>75370982</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="234" t="inlineStr">
+        <is>
+          <t>CPO696-3</t>
+        </is>
+      </c>
+      <c r="B92" s="234" t="inlineStr">
+        <is>
+          <t>2026.06.17</t>
+        </is>
+      </c>
+      <c r="C92" s="235" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D90" s="118" t="n">
-        <v>15289</v>
-      </c>
-      <c r="E90" s="118" t="n">
-        <v>101638</v>
-      </c>
-      <c r="F90" s="122" t="n">
-        <v>0.150426</v>
-      </c>
-      <c r="G90" s="118" t="n">
-        <v>1502.7</v>
-      </c>
-      <c r="H90" s="120" t="n">
-        <v>22974780</v>
-      </c>
-      <c r="I90" s="120" t="n">
-        <v>4521</v>
-      </c>
-      <c r="J90" s="120" t="n">
-        <v>1880</v>
-      </c>
-      <c r="K90" s="120" t="n">
-        <v>1203</v>
-      </c>
-      <c r="L90" s="121" t="n">
-        <v>22982384</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="116" t="inlineStr">
-        <is>
-          <t>CPO696-1</t>
-        </is>
-      </c>
-      <c r="B91" s="116" t="inlineStr">
-        <is>
-          <t>2026.05.29</t>
-        </is>
-      </c>
-      <c r="C91" s="117" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D91" s="118" t="n">
-        <v>78209</v>
-      </c>
-      <c r="E91" s="118" t="n">
-        <v>101638</v>
-      </c>
-      <c r="F91" s="122" t="n">
-        <v>0.769486</v>
-      </c>
-      <c r="G91" s="118" t="n">
-        <v>1502.7</v>
-      </c>
-      <c r="H91" s="120" t="n">
-        <v>117524664</v>
-      </c>
-      <c r="I91" s="120" t="n">
-        <v>23126</v>
-      </c>
-      <c r="J91" s="120" t="n">
-        <v>9619</v>
-      </c>
-      <c r="K91" s="120" t="n">
-        <v>6156</v>
-      </c>
-      <c r="L91" s="121" t="n">
-        <v>117563565</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="116" t="inlineStr">
-        <is>
-          <t>CPO696-2</t>
-        </is>
-      </c>
-      <c r="B92" s="116" t="inlineStr">
-        <is>
-          <t>2026.05.29</t>
-        </is>
-      </c>
-      <c r="C92" s="117" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D92" s="118" t="n">
-        <v>8140</v>
-      </c>
-      <c r="E92" s="118" t="n">
-        <v>101638</v>
-      </c>
-      <c r="F92" s="122" t="n">
-        <v>0.08008800000000001</v>
-      </c>
-      <c r="G92" s="118" t="n">
-        <v>1502.7</v>
-      </c>
-      <c r="H92" s="120" t="n">
-        <v>12231978</v>
-      </c>
-      <c r="I92" s="120" t="n">
-        <v>2407</v>
-      </c>
-      <c r="J92" s="120" t="n">
-        <v>1001</v>
-      </c>
-      <c r="K92" s="120" t="n">
-        <v>641</v>
-      </c>
-      <c r="L92" s="121" t="n">
-        <v>12236027</v>
+      <c r="D92" s="236" t="n">
+        <v>351274</v>
+      </c>
+      <c r="E92" s="236" t="n">
+        <v>351274</v>
+      </c>
+      <c r="F92" s="240">
+        <f>IFERROR(D92/E92,0)</f>
+        <v/>
+      </c>
+      <c r="G92" s="236" t="n">
+        <v>1518</v>
+      </c>
+      <c r="H92" s="238" t="n">
+        <v>533233932</v>
+      </c>
+      <c r="I92" s="238" t="n">
+        <v>30360</v>
+      </c>
+      <c r="J92" s="238" t="n">
+        <v>12500</v>
+      </c>
+      <c r="K92" s="238" t="n">
+        <v>8000</v>
+      </c>
+      <c r="L92" s="239">
+        <f>H92+I92+J92+K92</f>
+        <v/>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="234" t="inlineStr">
         <is>
-          <t>GPO481</t>
+          <t>APO001</t>
         </is>
       </c>
       <c r="B93" s="234" t="inlineStr">
         <is>
-          <t>2026.06.10</t>
+          <t>2026.06.17</t>
         </is>
       </c>
       <c r="C93" s="235" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Appotronics</t>
         </is>
       </c>
       <c r="D93" s="236" t="n">
-        <v>500</v>
+        <v>12400</v>
       </c>
       <c r="E93" s="236" t="n">
-        <v>119060</v>
-      </c>
-      <c r="F93" s="240" t="n">
-        <v>0.0042</v>
+        <v>12400</v>
+      </c>
+      <c r="F93" s="240">
+        <f>IFERROR(D93/E93,0)</f>
+        <v/>
       </c>
       <c r="G93" s="236" t="n">
-        <v>1525.3</v>
+        <v>1517.1</v>
       </c>
       <c r="H93" s="238" t="n">
-        <v>762650</v>
+        <v>18812040</v>
       </c>
       <c r="I93" s="238" t="n">
-        <v>128</v>
+        <v>30342</v>
       </c>
       <c r="J93" s="238" t="n">
-        <v>52</v>
+        <v>10000</v>
       </c>
       <c r="K93" s="238" t="n">
-        <v>34</v>
-      </c>
-      <c r="L93" s="239" t="n">
-        <v>762864</v>
+        <v>8000</v>
+      </c>
+      <c r="L93" s="239">
+        <f>H93+I93+J93+K93</f>
+        <v/>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="234" t="inlineStr">
         <is>
-          <t>GPO473-2</t>
+          <t>MPO67</t>
         </is>
       </c>
       <c r="B94" s="234" t="inlineStr">
         <is>
-          <t>2026.06.10</t>
+          <t>2026.06.17</t>
         </is>
       </c>
       <c r="C94" s="235" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D94" s="236" t="n">
-        <v>69160</v>
+        <v>49138.8</v>
       </c>
       <c r="E94" s="236" t="n">
-        <v>119060</v>
-      </c>
-      <c r="F94" s="240" t="n">
-        <v>0.580884</v>
+        <v>60726</v>
+      </c>
+      <c r="F94" s="240">
+        <f>IFERROR(D94/E94,0)</f>
+        <v/>
       </c>
       <c r="G94" s="236" t="n">
-        <v>1525.3</v>
+        <v>1517.3</v>
       </c>
       <c r="H94" s="238" t="n">
-        <v>105489748</v>
+        <v>74558330</v>
       </c>
       <c r="I94" s="238" t="n">
-        <v>17720</v>
+        <v>24555</v>
       </c>
       <c r="J94" s="238" t="n">
-        <v>7261</v>
+        <v>10115</v>
       </c>
       <c r="K94" s="238" t="n">
-        <v>4647</v>
-      </c>
-      <c r="L94" s="239" t="n">
-        <v>105519376</v>
+        <v>6473</v>
+      </c>
+      <c r="L94" s="239">
+        <f>H94+I94+J94+K94</f>
+        <v/>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="234" t="inlineStr">
         <is>
-          <t>GPO473-3</t>
+          <t>MPO68</t>
         </is>
       </c>
       <c r="B95" s="234" t="inlineStr">
         <is>
-          <t>2026.06.10</t>
+          <t>2026.06.17</t>
         </is>
       </c>
       <c r="C95" s="235" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D95" s="236" t="n">
-        <v>49400</v>
+        <v>11587.2</v>
       </c>
       <c r="E95" s="236" t="n">
-        <v>119060</v>
-      </c>
-      <c r="F95" s="240" t="n">
-        <v>0.414917</v>
+        <v>60726</v>
+      </c>
+      <c r="F95" s="240">
+        <f>IFERROR(D95/E95,0)</f>
+        <v/>
       </c>
       <c r="G95" s="236" t="n">
-        <v>1525.3</v>
+        <v>1517.3</v>
       </c>
       <c r="H95" s="238" t="n">
-        <v>75349820</v>
+        <v>17582284</v>
       </c>
       <c r="I95" s="238" t="n">
-        <v>12657</v>
+        <v>5791</v>
       </c>
       <c r="J95" s="238" t="n">
-        <v>5186</v>
+        <v>2385</v>
       </c>
       <c r="K95" s="238" t="n">
-        <v>3319</v>
-      </c>
-      <c r="L95" s="239" t="n">
-        <v>75370982</v>
+        <v>1527</v>
+      </c>
+      <c r="L95" s="239">
+        <f>H95+I95+J95+K95</f>
+        <v/>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="234" t="inlineStr">
         <is>
-          <t>CPO696-3</t>
+          <t>GPO475</t>
         </is>
       </c>
       <c r="B96" s="234" t="inlineStr">
@@ -17935,33 +17837,33 @@
       </c>
       <c r="C96" s="235" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D96" s="236" t="n">
-        <v>351274</v>
+        <v>540</v>
       </c>
       <c r="E96" s="236" t="n">
-        <v>351274</v>
+        <v>2040</v>
       </c>
       <c r="F96" s="240">
         <f>IFERROR(D96/E96,0)</f>
         <v/>
       </c>
       <c r="G96" s="236" t="n">
-        <v>1518</v>
+        <v>1516.8</v>
       </c>
       <c r="H96" s="238" t="n">
-        <v>533233932</v>
+        <v>819072</v>
       </c>
       <c r="I96" s="238" t="n">
-        <v>30360</v>
+        <v>8030</v>
       </c>
       <c r="J96" s="238" t="n">
-        <v>12500</v>
+        <v>1985</v>
       </c>
       <c r="K96" s="238" t="n">
-        <v>8000</v>
+        <v>2118</v>
       </c>
       <c r="L96" s="239">
         <f>H96+I96+J96+K96</f>
@@ -17971,7 +17873,7 @@
     <row r="97">
       <c r="A97" s="234" t="inlineStr">
         <is>
-          <t>APO001</t>
+          <t>GPO475-수리</t>
         </is>
       </c>
       <c r="B97" s="234" t="inlineStr">
@@ -17981,226 +17883,43 @@
       </c>
       <c r="C97" s="235" t="inlineStr">
         <is>
-          <t>Appotronics</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D97" s="236" t="n">
-        <v>12400</v>
+        <v>1500</v>
       </c>
       <c r="E97" s="236" t="n">
-        <v>12400</v>
+        <v>2040</v>
       </c>
       <c r="F97" s="240">
         <f>IFERROR(D97/E97,0)</f>
         <v/>
       </c>
       <c r="G97" s="236" t="n">
-        <v>1517.1</v>
+        <v>1516.8</v>
       </c>
       <c r="H97" s="238" t="n">
-        <v>18812040</v>
+        <v>2275200</v>
       </c>
       <c r="I97" s="238" t="n">
-        <v>30342</v>
+        <v>22306</v>
       </c>
       <c r="J97" s="238" t="n">
-        <v>10000</v>
+        <v>5515</v>
       </c>
       <c r="K97" s="238" t="n">
-        <v>8000</v>
+        <v>5882</v>
       </c>
       <c r="L97" s="239">
         <f>H97+I97+J97+K97</f>
         <v/>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="234" t="inlineStr">
-        <is>
-          <t>MPO67</t>
-        </is>
-      </c>
-      <c r="B98" s="234" t="inlineStr">
-        <is>
-          <t>2026.06.17</t>
-        </is>
-      </c>
-      <c r="C98" s="235" t="inlineStr">
-        <is>
-          <t>MAG</t>
-        </is>
-      </c>
-      <c r="D98" s="236" t="n">
-        <v>49138.8</v>
-      </c>
-      <c r="E98" s="236" t="n">
-        <v>60726</v>
-      </c>
-      <c r="F98" s="240">
-        <f>IFERROR(D98/E98,0)</f>
-        <v/>
-      </c>
-      <c r="G98" s="236" t="n">
-        <v>1517.3</v>
-      </c>
-      <c r="H98" s="238" t="n">
-        <v>74558330</v>
-      </c>
-      <c r="I98" s="238" t="n">
-        <v>24555</v>
-      </c>
-      <c r="J98" s="238" t="n">
-        <v>10115</v>
-      </c>
-      <c r="K98" s="238" t="n">
-        <v>6473</v>
-      </c>
-      <c r="L98" s="239">
-        <f>H98+I98+J98+K98</f>
-        <v/>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="234" t="inlineStr">
-        <is>
-          <t>MPO68</t>
-        </is>
-      </c>
-      <c r="B99" s="234" t="inlineStr">
-        <is>
-          <t>2026.06.17</t>
-        </is>
-      </c>
-      <c r="C99" s="235" t="inlineStr">
-        <is>
-          <t>MAG</t>
-        </is>
-      </c>
-      <c r="D99" s="236" t="n">
-        <v>11587.2</v>
-      </c>
-      <c r="E99" s="236" t="n">
-        <v>60726</v>
-      </c>
-      <c r="F99" s="240">
-        <f>IFERROR(D99/E99,0)</f>
-        <v/>
-      </c>
-      <c r="G99" s="236" t="n">
-        <v>1517.3</v>
-      </c>
-      <c r="H99" s="238" t="n">
-        <v>17582284</v>
-      </c>
-      <c r="I99" s="238" t="n">
-        <v>5791</v>
-      </c>
-      <c r="J99" s="238" t="n">
-        <v>2385</v>
-      </c>
-      <c r="K99" s="238" t="n">
-        <v>1527</v>
-      </c>
-      <c r="L99" s="239">
-        <f>H99+I99+J99+K99</f>
-        <v/>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="234" t="inlineStr">
-        <is>
-          <t>GPO475</t>
-        </is>
-      </c>
-      <c r="B100" s="234" t="inlineStr">
-        <is>
-          <t>2026.06.17</t>
-        </is>
-      </c>
-      <c r="C100" s="235" t="inlineStr">
-        <is>
-          <t>GDC</t>
-        </is>
-      </c>
-      <c r="D100" s="236" t="n">
-        <v>540</v>
-      </c>
-      <c r="E100" s="236" t="n">
-        <v>2040</v>
-      </c>
-      <c r="F100" s="240">
-        <f>IFERROR(D100/E100,0)</f>
-        <v/>
-      </c>
-      <c r="G100" s="236" t="n">
-        <v>1516.8</v>
-      </c>
-      <c r="H100" s="238" t="n">
-        <v>819072</v>
-      </c>
-      <c r="I100" s="238" t="n">
-        <v>8030</v>
-      </c>
-      <c r="J100" s="238" t="n">
-        <v>1985</v>
-      </c>
-      <c r="K100" s="238" t="n">
-        <v>2118</v>
-      </c>
-      <c r="L100" s="239">
-        <f>H100+I100+J100+K100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="234" t="inlineStr">
-        <is>
-          <t>GPO475-수리</t>
-        </is>
-      </c>
-      <c r="B101" s="234" t="inlineStr">
-        <is>
-          <t>2026.06.17</t>
-        </is>
-      </c>
-      <c r="C101" s="235" t="inlineStr">
-        <is>
-          <t>GDC</t>
-        </is>
-      </c>
-      <c r="D101" s="236" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E101" s="236" t="n">
-        <v>2040</v>
-      </c>
-      <c r="F101" s="240">
-        <f>IFERROR(D101/E101,0)</f>
-        <v/>
-      </c>
-      <c r="G101" s="236" t="n">
-        <v>1516.8</v>
-      </c>
-      <c r="H101" s="238" t="n">
-        <v>2275200</v>
-      </c>
-      <c r="I101" s="238" t="n">
-        <v>22306</v>
-      </c>
-      <c r="J101" s="238" t="n">
-        <v>5515</v>
-      </c>
-      <c r="K101" s="238" t="n">
-        <v>5882</v>
-      </c>
-      <c r="L101" s="239">
-        <f>H101+I101+J101+K101</f>
-        <v/>
-      </c>
-    </row>
+    <row r="98"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A45:L45"/>
+    <mergeCell ref="A41:L41"/>
     <mergeCell ref="A1:L1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/RNR_수입원가_2026_20260618.xlsx
+++ b/RNR_수입원가_2026_20260618.xlsx
@@ -2206,12 +2206,12 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="AE5" s="3" t="inlineStr">
+      <c r="AE5" s="175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF5" s="4" t="inlineStr">
+      <c r="AF5" s="174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2333,12 +2333,12 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="AE6" s="3" t="inlineStr">
+      <c r="AE6" s="175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF6" s="4" t="inlineStr">
+      <c r="AF6" s="174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2460,12 +2460,12 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="AE7" s="3" t="inlineStr">
+      <c r="AE7" s="175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF7" s="4" t="inlineStr">
+      <c r="AF7" s="174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2587,12 +2587,12 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="AE8" s="3" t="inlineStr">
+      <c r="AE8" s="175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF8" s="4" t="inlineStr">
+      <c r="AF8" s="174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2657,7 +2657,7 @@
           <t>Parts (국내)</t>
         </is>
       </c>
-      <c r="O9" s="12" t="n"/>
+      <c r="O9" s="177" t="n"/>
       <c r="P9" s="12" t="n"/>
       <c r="Q9" s="18">
         <f>IF(P9="","",IFERROR(VLOOKUP(O9,FxRateTable,4,TRUE),""))</f>
@@ -2673,7 +2673,7 @@
       <c r="T9" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="U9" s="13" t="n">
+      <c r="U9" s="176" t="n">
         <v>0</v>
       </c>
       <c r="V9" s="12" t="inlineStr">
@@ -2708,12 +2708,12 @@
         <v/>
       </c>
       <c r="AD9" s="12" t="n"/>
-      <c r="AE9" s="12" t="inlineStr">
+      <c r="AE9" s="177" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF9" s="13" t="inlineStr">
+      <c r="AF9" s="176" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2835,12 +2835,12 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="AE10" s="3" t="inlineStr">
+      <c r="AE10" s="175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF10" s="4" t="inlineStr">
+      <c r="AF10" s="174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2962,12 +2962,12 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="AE11" s="3" t="inlineStr">
+      <c r="AE11" s="175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF11" s="4" t="inlineStr">
+      <c r="AF11" s="174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3089,12 +3089,12 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AE12" s="3" t="inlineStr">
+      <c r="AE12" s="175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF12" s="4" t="inlineStr">
+      <c r="AF12" s="174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3216,12 +3216,12 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="AE13" s="3" t="inlineStr">
+      <c r="AE13" s="175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF13" s="4" t="inlineStr">
+      <c r="AF13" s="174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3343,12 +3343,12 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="AE14" s="3" t="inlineStr">
+      <c r="AE14" s="175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF14" s="4" t="inlineStr">
+      <c r="AF14" s="174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3470,12 +3470,12 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="AE15" s="3" t="inlineStr">
+      <c r="AE15" s="175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF15" s="4" t="inlineStr">
+      <c r="AF15" s="174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3597,12 +3597,12 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="AE16" s="3" t="inlineStr">
+      <c r="AE16" s="175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF16" s="4" t="inlineStr">
+      <c r="AF16" s="174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3724,12 +3724,12 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="AE17" s="3" t="inlineStr">
+      <c r="AE17" s="175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF17" s="4" t="inlineStr">
+      <c r="AF17" s="174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3851,12 +3851,12 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="AE18" s="3" t="inlineStr">
+      <c r="AE18" s="175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF18" s="4" t="inlineStr">
+      <c r="AF18" s="174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3978,12 +3978,12 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="AE19" s="3" t="inlineStr">
+      <c r="AE19" s="175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF19" s="4" t="inlineStr">
+      <c r="AF19" s="174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4105,12 +4105,12 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="AE20" s="3" t="inlineStr">
+      <c r="AE20" s="175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF20" s="4" t="inlineStr">
+      <c r="AF20" s="174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4232,12 +4232,12 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="AE21" s="3" t="inlineStr">
+      <c r="AE21" s="175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF21" s="4" t="inlineStr">
+      <c r="AF21" s="174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4359,12 +4359,12 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="AE22" s="3" t="inlineStr">
+      <c r="AE22" s="175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF22" s="4" t="inlineStr">
+      <c r="AF22" s="174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4429,7 +4429,7 @@
           <t>Projector (한국)</t>
         </is>
       </c>
-      <c r="O23" s="12" t="n"/>
+      <c r="O23" s="177" t="n"/>
       <c r="P23" s="12" t="n"/>
       <c r="Q23" s="18">
         <f>IF(P23="","",IFERROR(VLOOKUP(O23,FxRateTable,4,TRUE),""))</f>
@@ -4445,7 +4445,7 @@
       <c r="T23" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="U23" s="13" t="n">
+      <c r="U23" s="176" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="12" t="inlineStr">
@@ -4480,12 +4480,12 @@
         <v/>
       </c>
       <c r="AD23" s="12" t="n"/>
-      <c r="AE23" s="12" t="inlineStr">
+      <c r="AE23" s="177" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF23" s="13" t="inlineStr">
+      <c r="AF23" s="176" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4607,12 +4607,12 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AE24" s="3" t="inlineStr">
+      <c r="AE24" s="175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF24" s="4" t="inlineStr">
+      <c r="AF24" s="174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4734,12 +4734,12 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AE25" s="3" t="inlineStr">
+      <c r="AE25" s="175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF25" s="4" t="inlineStr">
+      <c r="AF25" s="174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4861,12 +4861,12 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AE26" s="3" t="inlineStr">
+      <c r="AE26" s="175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF26" s="4" t="inlineStr">
+      <c r="AF26" s="174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4988,12 +4988,12 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AE27" s="3" t="inlineStr">
+      <c r="AE27" s="175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF27" s="4" t="inlineStr">
+      <c r="AF27" s="174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5115,12 +5115,12 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AE28" s="3" t="inlineStr">
+      <c r="AE28" s="175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF28" s="4" t="inlineStr">
+      <c r="AF28" s="174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5238,8 +5238,8 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AE29" s="3" t="n"/>
-      <c r="AF29" s="4" t="n"/>
+      <c r="AE29" s="175" t="n"/>
+      <c r="AF29" s="174" t="n"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="78" t="n">
@@ -5353,8 +5353,8 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AE30" s="78" t="n"/>
-      <c r="AF30" s="78" t="n"/>
+      <c r="AE30" s="179" t="n"/>
+      <c r="AF30" s="179" t="n"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="78" t="n">
@@ -5468,8 +5468,8 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AE31" s="78" t="n"/>
-      <c r="AF31" s="78" t="n"/>
+      <c r="AE31" s="179" t="n"/>
+      <c r="AF31" s="179" t="n"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="78" t="n">
@@ -5573,8 +5573,8 @@
         <v/>
       </c>
       <c r="AD32" s="78" t="n"/>
-      <c r="AE32" s="78" t="n"/>
-      <c r="AF32" s="78" t="n"/>
+      <c r="AE32" s="179" t="n"/>
+      <c r="AF32" s="179" t="n"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="124" t="n">
@@ -5603,7 +5603,7 @@
       <c r="F33" s="181" t="n">
         <v>46127</v>
       </c>
-      <c r="G33" s="283" t="n">
+      <c r="G33" s="181" t="n">
         <v>46190</v>
       </c>
       <c r="H33" s="126" t="n">
@@ -5647,7 +5647,7 @@
       <c r="T33" s="128" t="n">
         <v>52140300</v>
       </c>
-      <c r="U33" s="129" t="n"/>
+      <c r="U33" s="182" t="n"/>
       <c r="V33" s="129" t="inlineStr">
         <is>
           <t>조운관세사무소</t>
@@ -5684,8 +5684,8 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AE33" s="129" t="n"/>
-      <c r="AF33" s="129" t="n"/>
+      <c r="AE33" s="182" t="n"/>
+      <c r="AF33" s="182" t="n"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="124" t="n">
@@ -5714,7 +5714,7 @@
       <c r="F34" s="181" t="n">
         <v>46143</v>
       </c>
-      <c r="G34" s="124" t="inlineStr">
+      <c r="G34" s="181" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5764,7 +5764,7 @@
       <c r="T34" s="128" t="n">
         <v>118665800</v>
       </c>
-      <c r="U34" s="129" t="n"/>
+      <c r="U34" s="182" t="n"/>
       <c r="V34" s="129" t="inlineStr">
         <is>
           <t>조운관세사무소</t>
@@ -5801,8 +5801,8 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="AE34" s="129" t="n"/>
-      <c r="AF34" s="129" t="n"/>
+      <c r="AE34" s="182" t="n"/>
+      <c r="AF34" s="182" t="n"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="124" t="n">
@@ -5875,7 +5875,7 @@
       <c r="T35" s="128" t="n">
         <v>14902330</v>
       </c>
-      <c r="U35" s="129" t="n"/>
+      <c r="U35" s="182" t="n"/>
       <c r="V35" s="129" t="inlineStr">
         <is>
           <t>조운관세사무소</t>
@@ -5912,8 +5912,8 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="AE35" s="129" t="n"/>
-      <c r="AF35" s="129" t="n"/>
+      <c r="AE35" s="182" t="n"/>
+      <c r="AF35" s="182" t="n"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="124" t="n">
@@ -5964,7 +5964,7 @@
         <v>7</v>
       </c>
       <c r="N36" s="129" t="n"/>
-      <c r="O36" s="129" t="n"/>
+      <c r="O36" s="182" t="n"/>
       <c r="P36" s="129" t="n"/>
       <c r="Q36" s="126">
         <f>IF(P36="","",IFERROR(VLOOKUP(O36,FxRateTable,4,TRUE),""))</f>
@@ -5980,7 +5980,7 @@
       <c r="T36" s="128" t="n">
         <v>0</v>
       </c>
-      <c r="U36" s="129" t="n"/>
+      <c r="U36" s="182" t="n"/>
       <c r="V36" s="129" t="n"/>
       <c r="W36" s="128" t="n">
         <v>0</v>
@@ -6009,8 +6009,8 @@
         <v/>
       </c>
       <c r="AD36" s="129" t="n"/>
-      <c r="AE36" s="129" t="n"/>
-      <c r="AF36" s="129" t="n"/>
+      <c r="AE36" s="182" t="n"/>
+      <c r="AF36" s="182" t="n"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="207" t="n">
@@ -6124,8 +6124,8 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="AE37" s="207" t="n"/>
-      <c r="AF37" s="208" t="n"/>
+      <c r="AE37" s="210" t="n"/>
+      <c r="AF37" s="209" t="n"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="207" t="n">
@@ -6239,8 +6239,8 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="AE38" s="207" t="n"/>
-      <c r="AF38" s="208" t="n"/>
+      <c r="AE38" s="210" t="n"/>
+      <c r="AF38" s="209" t="n"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="124" t="n">
@@ -6303,7 +6303,7 @@
           <t>JNIOR Model 410 (IPO017, FedEx 4/21 발송분)</t>
         </is>
       </c>
-      <c r="O39" s="129" t="n"/>
+      <c r="O39" s="182" t="n"/>
       <c r="P39" s="129" t="n"/>
       <c r="Q39" s="126">
         <f>IF(P39="","",IFERROR(VLOOKUP(O39,FxRateTable,4,TRUE),""))</f>
@@ -6319,7 +6319,7 @@
       <c r="T39" s="128" t="n">
         <v>0</v>
       </c>
-      <c r="U39" s="129" t="n"/>
+      <c r="U39" s="182" t="n"/>
       <c r="V39" s="129" t="inlineStr">
         <is>
           <t>-</t>
@@ -6352,12 +6352,12 @@
         <v/>
       </c>
       <c r="AD39" s="129" t="n"/>
-      <c r="AE39" s="129" t="inlineStr">
+      <c r="AE39" s="182" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF39" s="129" t="inlineStr">
+      <c r="AF39" s="182" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6390,7 +6390,7 @@
       <c r="F40" s="181" t="n">
         <v>46163</v>
       </c>
-      <c r="G40" s="283" t="inlineStr">
+      <c r="G40" s="181" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6444,7 +6444,7 @@
       <c r="T40" s="128" t="n">
         <v>52536040</v>
       </c>
-      <c r="U40" s="129" t="n"/>
+      <c r="U40" s="182" t="n"/>
       <c r="V40" s="129" t="inlineStr">
         <is>
           <t>조운관세사무소</t>
@@ -6481,8 +6481,8 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="AE40" s="129" t="n"/>
-      <c r="AF40" s="129" t="n"/>
+      <c r="AE40" s="182" t="n"/>
+      <c r="AF40" s="182" t="n"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="124" t="n">
@@ -6511,7 +6511,7 @@
       <c r="F41" s="181" t="n">
         <v>46154</v>
       </c>
-      <c r="G41" s="283" t="n">
+      <c r="G41" s="181" t="n">
         <v>46190</v>
       </c>
       <c r="H41" s="126" t="n">
@@ -6559,7 +6559,7 @@
       <c r="T41" s="128" t="n">
         <v>8891915</v>
       </c>
-      <c r="U41" s="129" t="n"/>
+      <c r="U41" s="182" t="n"/>
       <c r="V41" s="129" t="inlineStr">
         <is>
           <t>조운관세사무소</t>
@@ -6596,8 +6596,8 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="AE41" s="129" t="n"/>
-      <c r="AF41" s="129" t="n"/>
+      <c r="AE41" s="182" t="n"/>
+      <c r="AF41" s="182" t="n"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="124" t="n">
@@ -6626,7 +6626,7 @@
       <c r="F42" s="181" t="n">
         <v>46154</v>
       </c>
-      <c r="G42" s="283" t="n">
+      <c r="G42" s="181" t="n">
         <v>46190</v>
       </c>
       <c r="H42" s="126" t="n">
@@ -6674,7 +6674,7 @@
       <c r="T42" s="128" t="n">
         <v>2096763</v>
       </c>
-      <c r="U42" s="129" t="n"/>
+      <c r="U42" s="182" t="n"/>
       <c r="V42" s="129" t="inlineStr">
         <is>
           <t>조운관세사무소</t>
@@ -6711,8 +6711,8 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="AE42" s="129" t="n"/>
-      <c r="AF42" s="129" t="n"/>
+      <c r="AE42" s="182" t="n"/>
+      <c r="AF42" s="182" t="n"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="124" t="n">
@@ -6741,7 +6741,7 @@
       <c r="F43" s="181" t="n">
         <v>46163</v>
       </c>
-      <c r="G43" s="283" t="n">
+      <c r="G43" s="181" t="n">
         <v>46190</v>
       </c>
       <c r="H43" s="126" t="n">
@@ -6783,7 +6783,7 @@
       <c r="T43" s="128" t="n">
         <v>0</v>
       </c>
-      <c r="U43" s="129" t="n"/>
+      <c r="U43" s="182" t="n"/>
       <c r="V43" s="129" t="n"/>
       <c r="W43" s="128" t="n">
         <v>0</v>
@@ -6812,8 +6812,8 @@
         <v/>
       </c>
       <c r="AD43" s="129" t="n"/>
-      <c r="AE43" s="129" t="n"/>
-      <c r="AF43" s="129" t="n"/>
+      <c r="AE43" s="182" t="n"/>
+      <c r="AF43" s="182" t="n"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="20" t="n">
@@ -6868,7 +6868,7 @@
           <t>EW CP2220</t>
         </is>
       </c>
-      <c r="O44" s="20" t="inlineStr">
+      <c r="O44" s="184" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6892,7 +6892,7 @@
       <c r="T44" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="U44" s="21" t="n">
+      <c r="U44" s="183" t="n">
         <v>0</v>
       </c>
       <c r="V44" s="20" t="inlineStr">
@@ -6995,7 +6995,7 @@
           <t>HFR License</t>
         </is>
       </c>
-      <c r="O45" s="20" t="inlineStr">
+      <c r="O45" s="184" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7019,7 +7019,7 @@
       <c r="T45" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="U45" s="21" t="n">
+      <c r="U45" s="183" t="n">
         <v>0</v>
       </c>
       <c r="V45" s="20" t="inlineStr">
@@ -7122,7 +7122,7 @@
           <t>EW CP2309/2315/2320-RGB</t>
         </is>
       </c>
-      <c r="O46" s="20" t="inlineStr">
+      <c r="O46" s="184" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7146,7 +7146,7 @@
       <c r="T46" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="U46" s="21" t="n">
+      <c r="U46" s="183" t="n">
         <v>0</v>
       </c>
       <c r="V46" s="20" t="inlineStr">
@@ -7249,7 +7249,7 @@
           <t>TMS-2000 EW</t>
         </is>
       </c>
-      <c r="O47" s="20" t="inlineStr">
+      <c r="O47" s="184" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7273,7 +7273,7 @@
       <c r="T47" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="U47" s="21" t="n">
+      <c r="U47" s="183" t="n">
         <v>0</v>
       </c>
       <c r="V47" s="20" t="inlineStr">
@@ -7376,7 +7376,7 @@
           <t>TMS-1000 EW</t>
         </is>
       </c>
-      <c r="O48" s="20" t="inlineStr">
+      <c r="O48" s="184" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7400,7 +7400,7 @@
       <c r="T48" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="U48" s="21" t="n">
+      <c r="U48" s="183" t="n">
         <v>0</v>
       </c>
       <c r="V48" s="20" t="inlineStr">
@@ -7503,7 +7503,7 @@
           <t>EW 대량 (CP2208~CP4450)</t>
         </is>
       </c>
-      <c r="O49" s="20" t="inlineStr">
+      <c r="O49" s="184" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7527,7 +7527,7 @@
       <c r="T49" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="U49" s="21" t="n">
+      <c r="U49" s="183" t="n">
         <v>0</v>
       </c>
       <c r="V49" s="20" t="inlineStr">
@@ -7636,7 +7636,7 @@
           <t>EW 대량 (SR/SX/TMS)</t>
         </is>
       </c>
-      <c r="O50" s="20" t="inlineStr">
+      <c r="O50" s="184" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7660,7 +7660,7 @@
       <c r="T50" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="U50" s="21" t="n">
+      <c r="U50" s="183" t="n">
         <v>0</v>
       </c>
       <c r="V50" s="20" t="inlineStr">
@@ -7763,7 +7763,7 @@
           <t>EW CP2315/CP4440-RGB</t>
         </is>
       </c>
-      <c r="O51" s="20" t="inlineStr">
+      <c r="O51" s="184" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7787,7 +7787,7 @@
       <c r="T51" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="U51" s="21" t="n">
+      <c r="U51" s="183" t="n">
         <v>0</v>
       </c>
       <c r="V51" s="20" t="inlineStr">
@@ -7896,7 +7896,7 @@
           <t>EW (홀딩)</t>
         </is>
       </c>
-      <c r="O52" s="20" t="inlineStr">
+      <c r="O52" s="184" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7920,7 +7920,7 @@
       <c r="T52" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="U52" s="21" t="n">
+      <c r="U52" s="183" t="n">
         <v>0</v>
       </c>
       <c r="V52" s="20" t="inlineStr">
@@ -8023,7 +8023,7 @@
           <t>TMS-2000 License</t>
         </is>
       </c>
-      <c r="O53" s="20" t="inlineStr">
+      <c r="O53" s="184" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8047,7 +8047,7 @@
       <c r="T53" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="U53" s="21" t="n">
+      <c r="U53" s="183" t="n">
         <v>0</v>
       </c>
       <c r="V53" s="20" t="inlineStr">
@@ -8150,7 +8150,7 @@
           <t>SX/SR EW (CGV/Lotte)</t>
         </is>
       </c>
-      <c r="O54" s="20" t="inlineStr">
+      <c r="O54" s="184" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8174,7 +8174,7 @@
       <c r="T54" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="U54" s="21" t="n">
+      <c r="U54" s="183" t="n">
         <v>0</v>
       </c>
       <c r="V54" s="20" t="inlineStr">
@@ -8277,7 +8277,7 @@
           <t>SR-1000/SX-3000 EW</t>
         </is>
       </c>
-      <c r="O55" s="20" t="inlineStr">
+      <c r="O55" s="184" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8301,7 +8301,7 @@
       <c r="T55" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="U55" s="21" t="n">
+      <c r="U55" s="183" t="n">
         <v>0</v>
       </c>
       <c r="V55" s="20" t="inlineStr">
@@ -8404,7 +8404,7 @@
           <t>EW (메가박스 외)</t>
         </is>
       </c>
-      <c r="O56" s="20" t="inlineStr">
+      <c r="O56" s="184" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8428,7 +8428,7 @@
       <c r="T56" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="U56" s="21" t="n">
+      <c r="U56" s="183" t="n">
         <v>0</v>
       </c>
       <c r="V56" s="20" t="inlineStr">
@@ -8531,7 +8531,7 @@
           <t>SR/SX EW (하남미사 외)</t>
         </is>
       </c>
-      <c r="O57" s="20" t="inlineStr">
+      <c r="O57" s="184" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8555,7 +8555,7 @@
       <c r="T57" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="U57" s="21" t="n">
+      <c r="U57" s="183" t="n">
         <v>0</v>
       </c>
       <c r="V57" s="20" t="inlineStr">
@@ -8658,7 +8658,7 @@
           <t>TMS-1000 License</t>
         </is>
       </c>
-      <c r="O58" s="20" t="inlineStr">
+      <c r="O58" s="184" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8682,7 +8682,7 @@
       <c r="T58" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="U58" s="21" t="n">
+      <c r="U58" s="183" t="n">
         <v>0</v>
       </c>
       <c r="V58" s="20" t="inlineStr">
@@ -8785,7 +8785,7 @@
           <t>Dolby Atmos License</t>
         </is>
       </c>
-      <c r="O59" s="20" t="inlineStr">
+      <c r="O59" s="184" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8809,7 +8809,7 @@
       <c r="T59" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="U59" s="21" t="n">
+      <c r="U59" s="183" t="n">
         <v>0</v>
       </c>
       <c r="V59" s="20" t="inlineStr">
@@ -8912,7 +8912,7 @@
           <t>EW (CGV 동백 외)</t>
         </is>
       </c>
-      <c r="O60" s="20" t="inlineStr">
+      <c r="O60" s="184" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8936,7 +8936,7 @@
       <c r="T60" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="U60" s="21" t="n">
+      <c r="U60" s="183" t="n">
         <v>0</v>
       </c>
       <c r="V60" s="20" t="inlineStr">
@@ -9283,7 +9283,7 @@
         <v>8000</v>
       </c>
       <c r="N63" s="137" t="n"/>
-      <c r="O63" s="137" t="n"/>
+      <c r="O63" s="189" t="n"/>
       <c r="P63" s="137" t="n"/>
       <c r="Q63" s="134">
         <f>IF(P63="","",IFERROR(VLOOKUP(O63,FxRateTable,4,TRUE),""))</f>
@@ -9299,7 +9299,7 @@
       <c r="T63" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="U63" s="137" t="n"/>
+      <c r="U63" s="189" t="n"/>
       <c r="V63" s="137" t="n"/>
       <c r="W63" s="136" t="n">
         <v>0</v>
@@ -9388,7 +9388,7 @@
         <v>20</v>
       </c>
       <c r="N64" s="137" t="n"/>
-      <c r="O64" s="137" t="n"/>
+      <c r="O64" s="189" t="n"/>
       <c r="P64" s="137" t="n"/>
       <c r="Q64" s="134">
         <f>IF(P64="","",IFERROR(VLOOKUP(O64,FxRateTable,4,TRUE),""))</f>
@@ -9404,7 +9404,7 @@
       <c r="T64" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="U64" s="137" t="n"/>
+      <c r="U64" s="189" t="n"/>
       <c r="V64" s="137" t="n"/>
       <c r="W64" s="136" t="n">
         <v>0</v>
@@ -9471,7 +9471,7 @@
       <c r="F65" s="188" t="n">
         <v>46152</v>
       </c>
-      <c r="G65" s="233" t="n">
+      <c r="G65" s="188" t="n">
         <v>46183</v>
       </c>
       <c r="H65" s="134" t="n">
@@ -9493,7 +9493,7 @@
         <v>34</v>
       </c>
       <c r="N65" s="137" t="n"/>
-      <c r="O65" s="137" t="n"/>
+      <c r="O65" s="189" t="n"/>
       <c r="P65" s="137" t="n"/>
       <c r="Q65" s="134">
         <f>IF(P65="","",IFERROR(VLOOKUP(O65,FxRateTable,4,TRUE),""))</f>
@@ -9509,7 +9509,7 @@
       <c r="T65" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="U65" s="137" t="n"/>
+      <c r="U65" s="189" t="n"/>
       <c r="V65" s="137" t="n"/>
       <c r="W65" s="136" t="n">
         <v>0</v>
@@ -9542,12 +9542,12 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="AE65" s="137" t="inlineStr">
+      <c r="AE65" s="189" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF65" s="137" t="inlineStr">
+      <c r="AF65" s="189" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9606,7 +9606,7 @@
           <t>TMS-1000 License 6 screens (CGV 안동)</t>
         </is>
       </c>
-      <c r="O66" s="137" t="n"/>
+      <c r="O66" s="189" t="n"/>
       <c r="P66" s="137" t="n"/>
       <c r="Q66" s="134">
         <f>IF(P66="","",IFERROR(VLOOKUP(O66,FxRateTable,4,TRUE),""))</f>
@@ -9622,7 +9622,7 @@
       <c r="T66" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="U66" s="137" t="n"/>
+      <c r="U66" s="189" t="n"/>
       <c r="V66" s="137" t="n"/>
       <c r="W66" s="136" t="n">
         <v>0</v>
@@ -9721,7 +9721,7 @@
           <t>Inspection fee</t>
         </is>
       </c>
-      <c r="O67" s="12" t="inlineStr">
+      <c r="O67" s="177" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9745,7 +9745,7 @@
       <c r="T67" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="U67" s="13" t="n">
+      <c r="U67" s="176" t="n">
         <v>0</v>
       </c>
       <c r="V67" s="12" t="inlineStr">
@@ -9874,7 +9874,7 @@
       <c r="T68" s="18" t="n">
         <v>67750</v>
       </c>
-      <c r="U68" s="13" t="n"/>
+      <c r="U68" s="176" t="n"/>
       <c r="V68" s="12" t="inlineStr">
         <is>
           <t>운서합동</t>
@@ -10027,8 +10027,8 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="AE69" s="216" t="n"/>
-      <c r="AF69" s="217" t="n"/>
+      <c r="AE69" s="219" t="n"/>
+      <c r="AF69" s="218" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="284" t="n">
@@ -10099,7 +10099,7 @@
       <c r="T70" s="290" t="n">
         <v>0</v>
       </c>
-      <c r="U70" s="285" t="n"/>
+      <c r="U70" s="286" t="n"/>
       <c r="V70" s="284" t="n"/>
       <c r="W70" s="290" t="n">
         <v>0</v>
@@ -13494,7 +13494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M98"/>
+  <dimension ref="A1:M97"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="12.83203125" customWidth="1" style="160" min="1" max="1"/>
@@ -17916,7 +17916,6 @@
         <v/>
       </c>
     </row>
-    <row r="98"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A41:L41"/>
